--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB290"/>
+  <dimension ref="A1:AB292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26229,6 +26229,186 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="C291" t="n">
+        <v>339.94</v>
+      </c>
+      <c r="D291" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="E291" t="n">
+        <v>401.14</v>
+      </c>
+      <c r="F291" t="n">
+        <v>409.83</v>
+      </c>
+      <c r="G291" t="n">
+        <v>418.36</v>
+      </c>
+      <c r="H291" t="n">
+        <v>424.68</v>
+      </c>
+      <c r="I291" t="n">
+        <v>420.47</v>
+      </c>
+      <c r="J291" t="n">
+        <v>425.07</v>
+      </c>
+      <c r="K291" t="n">
+        <v>424.63</v>
+      </c>
+      <c r="L291" t="n">
+        <v>419.06</v>
+      </c>
+      <c r="M291" t="n">
+        <v>419.7</v>
+      </c>
+      <c r="N291" t="n">
+        <v>427.98</v>
+      </c>
+      <c r="O291" t="n">
+        <v>424.18</v>
+      </c>
+      <c r="P291" t="n">
+        <v>427.11</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>430.04</v>
+      </c>
+      <c r="R291" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="S291" t="n">
+        <v>426.38</v>
+      </c>
+      <c r="T291" t="n">
+        <v>411.61</v>
+      </c>
+      <c r="U291" t="n">
+        <v>403.04</v>
+      </c>
+      <c r="V291" t="n">
+        <v>404.08</v>
+      </c>
+      <c r="W291" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="X291" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>393.33</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="C292" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="D292" t="n">
+        <v>359.21</v>
+      </c>
+      <c r="E292" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="F292" t="n">
+        <v>407.69</v>
+      </c>
+      <c r="G292" t="n">
+        <v>413.57</v>
+      </c>
+      <c r="H292" t="n">
+        <v>419.62</v>
+      </c>
+      <c r="I292" t="n">
+        <v>416.04</v>
+      </c>
+      <c r="J292" t="n">
+        <v>419.4</v>
+      </c>
+      <c r="K292" t="n">
+        <v>420.08</v>
+      </c>
+      <c r="L292" t="n">
+        <v>413.52</v>
+      </c>
+      <c r="M292" t="n">
+        <v>414.65</v>
+      </c>
+      <c r="N292" t="n">
+        <v>422.32</v>
+      </c>
+      <c r="O292" t="n">
+        <v>419.01</v>
+      </c>
+      <c r="P292" t="n">
+        <v>427.11</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>425.56</v>
+      </c>
+      <c r="R292" t="n">
+        <v>425.37</v>
+      </c>
+      <c r="S292" t="n">
+        <v>421.21</v>
+      </c>
+      <c r="T292" t="n">
+        <v>407.84</v>
+      </c>
+      <c r="U292" t="n">
+        <v>399.96</v>
+      </c>
+      <c r="V292" t="n">
+        <v>401.71</v>
+      </c>
+      <c r="W292" t="n">
+        <v>403.55</v>
+      </c>
+      <c r="X292" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>379.94</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26240,7 +26420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29243,6 +29423,26 @@
       </c>
       <c r="B300" t="n">
         <v>1.67</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -29411,28 +29611,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6562938713546884</v>
+        <v>-0.8512114742251935</v>
       </c>
       <c r="J2" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K2" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005634696237864723</v>
+        <v>0.009345301534280925</v>
       </c>
       <c r="M2" t="n">
-        <v>53.64045848581106</v>
+        <v>54.46633971319853</v>
       </c>
       <c r="N2" t="n">
-        <v>4160.600242746234</v>
+        <v>4246.855531159767</v>
       </c>
       <c r="O2" t="n">
-        <v>64.50271500290692</v>
+        <v>65.16790261439881</v>
       </c>
       <c r="P2" t="n">
-        <v>499.1651379541156</v>
+        <v>501.117473638003</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29489,28 +29689,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8612590718492175</v>
+        <v>-1.090062599292947</v>
       </c>
       <c r="J3" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008808029168695275</v>
+        <v>0.01379299805458267</v>
       </c>
       <c r="M3" t="n">
-        <v>51.86104565029289</v>
+        <v>52.90848701158441</v>
       </c>
       <c r="N3" t="n">
-        <v>4193.168727691281</v>
+        <v>4310.569311991815</v>
       </c>
       <c r="O3" t="n">
-        <v>64.7546811257015</v>
+        <v>65.65492602990133</v>
       </c>
       <c r="P3" t="n">
-        <v>501.8646557788661</v>
+        <v>504.3182868322177</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29567,28 +29767,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4202058602737229</v>
+        <v>-0.6062028986087586</v>
       </c>
       <c r="J4" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K4" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002170451989400912</v>
+        <v>0.004476186456407349</v>
       </c>
       <c r="M4" t="n">
-        <v>51.95791953184543</v>
+        <v>52.73985917895792</v>
       </c>
       <c r="N4" t="n">
-        <v>4326.349568787053</v>
+        <v>4399.252158444514</v>
       </c>
       <c r="O4" t="n">
-        <v>65.77499197101473</v>
+        <v>66.32685849973986</v>
       </c>
       <c r="P4" t="n">
-        <v>492.5895424920523</v>
+        <v>494.4954581517227</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29645,28 +29845,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2260828688245419</v>
+        <v>0.09089160217572513</v>
       </c>
       <c r="J5" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K5" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007479098325541278</v>
+        <v>0.0001211365927128449</v>
       </c>
       <c r="M5" t="n">
-        <v>48.37092579001883</v>
+        <v>48.86501418880106</v>
       </c>
       <c r="N5" t="n">
-        <v>3720.925819406361</v>
+        <v>3750.416560183296</v>
       </c>
       <c r="O5" t="n">
-        <v>60.99939195931679</v>
+        <v>61.24064467478519</v>
       </c>
       <c r="P5" t="n">
-        <v>481.3538184719285</v>
+        <v>482.7341122745097</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29723,28 +29923,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>1.026592990707798</v>
+        <v>0.9118106067374844</v>
       </c>
       <c r="J6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K6" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01714998913845811</v>
+        <v>0.01361387190188945</v>
       </c>
       <c r="M6" t="n">
-        <v>43.80333313696656</v>
+        <v>44.30637017559496</v>
       </c>
       <c r="N6" t="n">
-        <v>3207.772275525901</v>
+        <v>3228.212359755425</v>
       </c>
       <c r="O6" t="n">
-        <v>56.63719869066532</v>
+        <v>56.81735966899047</v>
       </c>
       <c r="P6" t="n">
-        <v>460.6894605055562</v>
+        <v>461.8778745987543</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29801,28 +30001,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.535724011592961</v>
+        <v>1.422142026443832</v>
       </c>
       <c r="J7" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K7" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04219860748439463</v>
+        <v>0.03643452439161809</v>
       </c>
       <c r="M7" t="n">
-        <v>40.81085306038835</v>
+        <v>40.96478495541197</v>
       </c>
       <c r="N7" t="n">
-        <v>2805.182379553657</v>
+        <v>2827.624524927437</v>
       </c>
       <c r="O7" t="n">
-        <v>52.96397246764689</v>
+        <v>53.17541278567978</v>
       </c>
       <c r="P7" t="n">
-        <v>453.7299130896574</v>
+        <v>454.922612796942</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29879,28 +30079,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4174147802465</v>
+        <v>1.336632704497955</v>
       </c>
       <c r="J8" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K8" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06238578377222681</v>
+        <v>0.05595657848542179</v>
       </c>
       <c r="M8" t="n">
-        <v>32.17219854993274</v>
+        <v>32.25847386414426</v>
       </c>
       <c r="N8" t="n">
-        <v>1600.799268515799</v>
+        <v>1611.953989750332</v>
       </c>
       <c r="O8" t="n">
-        <v>40.00998960904388</v>
+        <v>40.14914681223415</v>
       </c>
       <c r="P8" t="n">
-        <v>442.3480691600831</v>
+        <v>443.1851839775688</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29957,28 +30157,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7268230230781169</v>
+        <v>0.6806552686789267</v>
       </c>
       <c r="J9" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02938303470999659</v>
+        <v>0.02605965264461085</v>
       </c>
       <c r="M9" t="n">
-        <v>24.9375402839539</v>
+        <v>24.94763259610916</v>
       </c>
       <c r="N9" t="n">
-        <v>917.5338094999009</v>
+        <v>918.3539404923579</v>
       </c>
       <c r="O9" t="n">
-        <v>30.29082054847476</v>
+        <v>30.30435514067834</v>
       </c>
       <c r="P9" t="n">
-        <v>431.6904274000997</v>
+        <v>432.1725080140322</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30035,28 +30235,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4919297484695889</v>
+        <v>0.4778935397937786</v>
       </c>
       <c r="J10" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K10" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02628039240517088</v>
+        <v>0.02517985641976095</v>
       </c>
       <c r="M10" t="n">
-        <v>18.22922828262466</v>
+        <v>18.17568261304084</v>
       </c>
       <c r="N10" t="n">
-        <v>475.996121594481</v>
+        <v>473.3626002243302</v>
       </c>
       <c r="O10" t="n">
-        <v>21.81733534587762</v>
+        <v>21.75689776195885</v>
       </c>
       <c r="P10" t="n">
-        <v>419.2303554146694</v>
+        <v>419.3769900622649</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30113,28 +30313,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5483053694201075</v>
+        <v>0.542261933777198</v>
       </c>
       <c r="J11" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K11" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0415534164088972</v>
+        <v>0.04127100273497497</v>
       </c>
       <c r="M11" t="n">
-        <v>15.14885086324058</v>
+        <v>15.06962752605281</v>
       </c>
       <c r="N11" t="n">
-        <v>368.9718535186424</v>
+        <v>366.5711383322845</v>
       </c>
       <c r="O11" t="n">
-        <v>19.20864007468104</v>
+        <v>19.14604759035881</v>
       </c>
       <c r="P11" t="n">
-        <v>412.2970837079504</v>
+        <v>412.3598445432814</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30191,28 +30391,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4264535028784393</v>
+        <v>0.4368488334073226</v>
       </c>
       <c r="J12" t="n">
+        <v>291</v>
+      </c>
+      <c r="K12" t="n">
         <v>289</v>
       </c>
-      <c r="K12" t="n">
-        <v>287</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.02665316661064043</v>
+        <v>0.02832515243182776</v>
       </c>
       <c r="M12" t="n">
-        <v>15.06017711604331</v>
+        <v>15.01711212905681</v>
       </c>
       <c r="N12" t="n">
-        <v>349.2787137070653</v>
+        <v>347.2798593274158</v>
       </c>
       <c r="O12" t="n">
-        <v>18.68899980488697</v>
+        <v>18.63544631414595</v>
       </c>
       <c r="P12" t="n">
-        <v>397.7788744436255</v>
+        <v>397.6703350547289</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30269,28 +30469,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2415521399103221</v>
+        <v>0.2690992921068935</v>
       </c>
       <c r="J13" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K13" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009418075339226228</v>
+        <v>0.01175107292020494</v>
       </c>
       <c r="M13" t="n">
-        <v>14.73213102641997</v>
+        <v>14.7779159981571</v>
       </c>
       <c r="N13" t="n">
-        <v>316.7895023809821</v>
+        <v>317.1209457888668</v>
       </c>
       <c r="O13" t="n">
-        <v>17.79858147103252</v>
+        <v>17.8078899869936</v>
       </c>
       <c r="P13" t="n">
-        <v>391.7125030848866</v>
+        <v>391.4208979989697</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30347,28 +30547,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01833368804672436</v>
+        <v>0.02885746070464317</v>
       </c>
       <c r="J14" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K14" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L14" t="n">
-        <v>5.315165481190043e-05</v>
+        <v>0.0001307906733565289</v>
       </c>
       <c r="M14" t="n">
-        <v>15.43757169817272</v>
+        <v>15.60969701118383</v>
       </c>
       <c r="N14" t="n">
-        <v>325.4681397370464</v>
+        <v>330.5530250626308</v>
       </c>
       <c r="O14" t="n">
-        <v>18.04073556529906</v>
+        <v>18.18111726662118</v>
       </c>
       <c r="P14" t="n">
-        <v>392.8609751617839</v>
+        <v>392.3610266509488</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30425,28 +30625,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5331936549716786</v>
+        <v>-0.478954545993487</v>
       </c>
       <c r="J15" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K15" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03606171630407851</v>
+        <v>0.02904640468607145</v>
       </c>
       <c r="M15" t="n">
-        <v>16.25694086744386</v>
+        <v>16.44678196396885</v>
       </c>
       <c r="N15" t="n">
-        <v>402.2860659437545</v>
+        <v>409.5041346440559</v>
       </c>
       <c r="O15" t="n">
-        <v>20.05707022333408</v>
+        <v>20.23620850465956</v>
       </c>
       <c r="P15" t="n">
-        <v>397.1470681709049</v>
+        <v>396.5848556771869</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30503,28 +30703,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6005134845386215</v>
+        <v>-0.5324094433182455</v>
       </c>
       <c r="J16" t="n">
+        <v>291</v>
+      </c>
+      <c r="K16" t="n">
         <v>289</v>
       </c>
-      <c r="K16" t="n">
-        <v>287</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.05859843582008739</v>
+        <v>0.04513327571041814</v>
       </c>
       <c r="M16" t="n">
-        <v>13.53124452783399</v>
+        <v>13.81497755238768</v>
       </c>
       <c r="N16" t="n">
-        <v>306.0677009437545</v>
+        <v>319.6019062905034</v>
       </c>
       <c r="O16" t="n">
-        <v>17.49479068019262</v>
+        <v>17.87741329976189</v>
       </c>
       <c r="P16" t="n">
-        <v>394.7335914297202</v>
+        <v>394.0257583157619</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30581,28 +30781,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7507343709356119</v>
+        <v>-0.6799263456471314</v>
       </c>
       <c r="J17" t="n">
+        <v>291</v>
+      </c>
+      <c r="K17" t="n">
         <v>289</v>
       </c>
-      <c r="K17" t="n">
-        <v>287</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.08750843870417646</v>
+        <v>0.07037507858084247</v>
       </c>
       <c r="M17" t="n">
-        <v>13.85048665492508</v>
+        <v>14.10859037688262</v>
       </c>
       <c r="N17" t="n">
-        <v>311.4241089685144</v>
+        <v>326.4014151145705</v>
       </c>
       <c r="O17" t="n">
-        <v>17.64721249853683</v>
+        <v>18.0665828289295</v>
       </c>
       <c r="P17" t="n">
-        <v>397.188464814833</v>
+        <v>396.4526182899847</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30659,28 +30859,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.018933193262219</v>
+        <v>-0.9503469662451115</v>
       </c>
       <c r="J18" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K18" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205926685423369</v>
+        <v>0.1043135149891806</v>
       </c>
       <c r="M18" t="n">
-        <v>15.99137301378381</v>
+        <v>16.19055085482044</v>
       </c>
       <c r="N18" t="n">
-        <v>402.0182854624564</v>
+        <v>415.352055062328</v>
       </c>
       <c r="O18" t="n">
-        <v>20.05039364856601</v>
+        <v>20.38018780733701</v>
       </c>
       <c r="P18" t="n">
-        <v>405.5438380707651</v>
+        <v>404.8329806744352</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30737,28 +30937,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8004250506308763</v>
+        <v>-0.7409827475826237</v>
       </c>
       <c r="J19" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K19" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1004455363986489</v>
+        <v>0.08546440360310614</v>
       </c>
       <c r="M19" t="n">
-        <v>13.45086922367322</v>
+        <v>13.57994462384601</v>
       </c>
       <c r="N19" t="n">
-        <v>303.6118078216531</v>
+        <v>313.5988837340555</v>
       </c>
       <c r="O19" t="n">
-        <v>17.42446004390532</v>
+        <v>17.70872337956792</v>
       </c>
       <c r="P19" t="n">
-        <v>402.4456374061096</v>
+        <v>401.8285793497511</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30815,28 +31015,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6557220258082047</v>
+        <v>-0.6104233799230599</v>
       </c>
       <c r="J20" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K20" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07117417176549967</v>
+        <v>0.06180974207059886</v>
       </c>
       <c r="M20" t="n">
-        <v>13.78072569111394</v>
+        <v>13.9073070253574</v>
       </c>
       <c r="N20" t="n">
-        <v>296.9148357340113</v>
+        <v>301.883428585651</v>
       </c>
       <c r="O20" t="n">
-        <v>17.23121689649374</v>
+        <v>17.37479290770543</v>
       </c>
       <c r="P20" t="n">
-        <v>394.6535457699685</v>
+        <v>394.1833094224989</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30893,28 +31093,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3574318644457766</v>
+        <v>-0.3242357071211872</v>
       </c>
       <c r="J21" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K21" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02360955650068475</v>
+        <v>0.01954922691961003</v>
       </c>
       <c r="M21" t="n">
-        <v>13.70951650766758</v>
+        <v>13.76435427162453</v>
       </c>
       <c r="N21" t="n">
-        <v>279.577821821043</v>
+        <v>281.4238205149983</v>
       </c>
       <c r="O21" t="n">
-        <v>16.72058078599673</v>
+        <v>16.77569135728833</v>
       </c>
       <c r="P21" t="n">
-        <v>387.232619364786</v>
+        <v>386.888017682842</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30971,28 +31171,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2638684088856198</v>
+        <v>-0.2221362217533905</v>
       </c>
       <c r="J22" t="n">
+        <v>291</v>
+      </c>
+      <c r="K22" t="n">
         <v>289</v>
       </c>
-      <c r="K22" t="n">
-        <v>287</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01033364336475651</v>
+        <v>0.007336017442038933</v>
       </c>
       <c r="M22" t="n">
-        <v>15.62092365269992</v>
+        <v>15.73570525945762</v>
       </c>
       <c r="N22" t="n">
-        <v>352.8260761489448</v>
+        <v>356.3346059515583</v>
       </c>
       <c r="O22" t="n">
-        <v>18.78366514152509</v>
+        <v>18.87682722153165</v>
       </c>
       <c r="P22" t="n">
-        <v>380.1709959773933</v>
+        <v>379.7365884011855</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31049,28 +31249,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0400672378625315</v>
+        <v>0.003395412665435605</v>
       </c>
       <c r="J23" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K23" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0002477390940285318</v>
+        <v>1.77372151277666e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>15.39480990074039</v>
+        <v>15.53314410269664</v>
       </c>
       <c r="N23" t="n">
-        <v>343.2263171076482</v>
+        <v>347.3033880567482</v>
       </c>
       <c r="O23" t="n">
-        <v>18.52636815751129</v>
+        <v>18.63607759311889</v>
       </c>
       <c r="P23" t="n">
-        <v>373.757300496738</v>
+        <v>373.3046499685412</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31127,28 +31327,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1210846908585015</v>
+        <v>0.1530581736080436</v>
       </c>
       <c r="J24" t="n">
+        <v>291</v>
+      </c>
+      <c r="K24" t="n">
         <v>289</v>
       </c>
-      <c r="K24" t="n">
-        <v>287</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.00233916104578813</v>
+        <v>0.003750839915765414</v>
       </c>
       <c r="M24" t="n">
-        <v>15.23108528040846</v>
+        <v>15.27721735769845</v>
       </c>
       <c r="N24" t="n">
-        <v>332.3061914296292</v>
+        <v>333.5129936200074</v>
       </c>
       <c r="O24" t="n">
-        <v>18.2292674408389</v>
+        <v>18.26233812029575</v>
       </c>
       <c r="P24" t="n">
-        <v>368.6293448052058</v>
+        <v>368.2975603961924</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31205,28 +31405,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2690761141582455</v>
+        <v>0.2897116228683274</v>
       </c>
       <c r="J25" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K25" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01323262322645868</v>
+        <v>0.01546540919654382</v>
       </c>
       <c r="M25" t="n">
-        <v>14.29296900787939</v>
+        <v>14.29478981212105</v>
       </c>
       <c r="N25" t="n">
-        <v>286.5421159435898</v>
+        <v>286.0318198271528</v>
       </c>
       <c r="O25" t="n">
-        <v>16.9275549310463</v>
+        <v>16.91247527203374</v>
       </c>
       <c r="P25" t="n">
-        <v>370.3817107675603</v>
+        <v>370.1676848745631</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31283,28 +31483,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3609923982078919</v>
+        <v>0.3698924016737358</v>
       </c>
       <c r="J26" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K26" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02028349303109189</v>
+        <v>0.02158505095474383</v>
       </c>
       <c r="M26" t="n">
-        <v>15.33443475834325</v>
+        <v>15.26514757428981</v>
       </c>
       <c r="N26" t="n">
-        <v>333.208444897276</v>
+        <v>331.1954966185256</v>
       </c>
       <c r="O26" t="n">
-        <v>18.25399805240693</v>
+        <v>18.19877733856111</v>
       </c>
       <c r="P26" t="n">
-        <v>365.7602531361496</v>
+        <v>365.6680086035919</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31361,28 +31561,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2748489902946104</v>
+        <v>0.2742816809251358</v>
       </c>
       <c r="J27" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K27" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0122842872495571</v>
+        <v>0.01242437290547782</v>
       </c>
       <c r="M27" t="n">
-        <v>15.28532667129083</v>
+        <v>15.19115949284535</v>
       </c>
       <c r="N27" t="n">
-        <v>321.5381431287998</v>
+        <v>319.3398311544977</v>
       </c>
       <c r="O27" t="n">
-        <v>17.93148468835751</v>
+        <v>17.87008201308818</v>
       </c>
       <c r="P27" t="n">
-        <v>362.4022609533557</v>
+        <v>362.4081527464047</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31420,7 +31620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB290"/>
+  <dimension ref="A1:AB292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71895,6 +72095,290 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>-37.79781068352882,174.84147746219898</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>-37.797127956300365,174.84110622204577</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>-37.79672486873729,174.8403202451502</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-37.7963920208646,174.83943008724387</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-37.79589384186426,174.83877907416388</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-37.79538739084581,174.8381372996048</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-37.794869285426856,174.8375191520122</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>-37.79423614601473,174.8369431607663</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-37.79351996682551,174.8364631880063</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-37.792799015116,174.83619315786814</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-37.79208184182479,174.83598827771343</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-37.791333383321465,174.83578209837594</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-37.79059521603271,174.8356169779809</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-37.78988087395822,174.83559403913668</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-37.78916725337981,174.83550487628034</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>-37.788456196473476,174.83542669829455</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>-37.787756752739,174.83538358582757</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>-37.78707135065196,174.83535633426737</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>-37.786363587968324,174.83540929563753</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>-37.78564842926924,174.8353899047113</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>-37.78494336926433,174.8352630564</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>-37.784235705446356,174.8351627644729</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>-37.78352080335642,174.83515154231952</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>-37.78282402183188,174.8350681658225</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>-37.782118414468464,174.83502003383015</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>-37.78139890978382,174.83499136989593</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-37.79772666752648,174.8416020654736</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-37.797101176273685,174.8411459390814</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-37.79669388814507,174.84036619232066</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-37.7963713673136,174.83946071876292</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-37.79588145440688,174.838797695665</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-37.79535992978988,174.8381792589132</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-37.79484032461544,174.83756352614608</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-37.79421471711711,174.83698559815574</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-37.79350138607619,174.83652315875926</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-37.79278679502257,174.8362424716505</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-37.79206896493844,174.83604905110624</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-37.79132648600827,174.8358387740449</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-37.79059084633076,174.83568100524965</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-37.78987714840932,174.83565255069027</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-37.78916725337981,174.83550487628034</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-37.788453674757356,174.8354774633722</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-37.787753533101636,174.83543588214897</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>-37.78706590883576,174.83541462974173</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>-37.786358786850684,174.83545166807656</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>-37.78564452134349,174.8354245242479</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>-37.78494047815655,174.8352897155816</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>-37.784235705446356,174.8351627644729</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>-37.78351942788359,174.83516471168048</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>-37.78282046339992,174.8350952713022</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>-37.782112850229346,174.83505510088779</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>-37.78139317756069,174.83502743624973</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB292"/>
+  <dimension ref="A1:AB294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26409,6 +26409,186 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>343.79</v>
+      </c>
+      <c r="C293" t="n">
+        <v>337.58</v>
+      </c>
+      <c r="D293" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="E293" t="n">
+        <v>397.58</v>
+      </c>
+      <c r="F293" t="n">
+        <v>406.44</v>
+      </c>
+      <c r="G293" t="n">
+        <v>415.33</v>
+      </c>
+      <c r="H293" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I293" t="n">
+        <v>412.21</v>
+      </c>
+      <c r="J293" t="n">
+        <v>415.99</v>
+      </c>
+      <c r="K293" t="n">
+        <v>417.63</v>
+      </c>
+      <c r="L293" t="n">
+        <v>411.4</v>
+      </c>
+      <c r="M293" t="n">
+        <v>413.81</v>
+      </c>
+      <c r="N293" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="O293" t="n">
+        <v>420.91</v>
+      </c>
+      <c r="P293" t="n">
+        <v>428.81</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>428.04</v>
+      </c>
+      <c r="R293" t="n">
+        <v>426.98</v>
+      </c>
+      <c r="S293" t="n">
+        <v>422.05</v>
+      </c>
+      <c r="T293" t="n">
+        <v>409.41</v>
+      </c>
+      <c r="U293" t="n">
+        <v>402.58</v>
+      </c>
+      <c r="V293" t="n">
+        <v>405.01</v>
+      </c>
+      <c r="W293" t="n">
+        <v>408.56</v>
+      </c>
+      <c r="X293" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>343.42</v>
+      </c>
+      <c r="C294" t="n">
+        <v>340.06</v>
+      </c>
+      <c r="D294" t="n">
+        <v>362.08</v>
+      </c>
+      <c r="E294" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="F294" t="n">
+        <v>407.54</v>
+      </c>
+      <c r="G294" t="n">
+        <v>415.84</v>
+      </c>
+      <c r="H294" t="n">
+        <v>416.81</v>
+      </c>
+      <c r="I294" t="n">
+        <v>411.23</v>
+      </c>
+      <c r="J294" t="n">
+        <v>414.86</v>
+      </c>
+      <c r="K294" t="n">
+        <v>415.65</v>
+      </c>
+      <c r="L294" t="n">
+        <v>409.96</v>
+      </c>
+      <c r="M294" t="n">
+        <v>414.6</v>
+      </c>
+      <c r="N294" t="n">
+        <v>423.42</v>
+      </c>
+      <c r="O294" t="n">
+        <v>421.91</v>
+      </c>
+      <c r="P294" t="n">
+        <v>429.01</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>429.25</v>
+      </c>
+      <c r="R294" t="n">
+        <v>427.69</v>
+      </c>
+      <c r="S294" t="n">
+        <v>421.78</v>
+      </c>
+      <c r="T294" t="n">
+        <v>410.99</v>
+      </c>
+      <c r="U294" t="n">
+        <v>404.88</v>
+      </c>
+      <c r="V294" t="n">
+        <v>407.51</v>
+      </c>
+      <c r="W294" t="n">
+        <v>410.84</v>
+      </c>
+      <c r="X294" t="n">
+        <v>399.36</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>393.67</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26420,7 +26600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29443,6 +29623,26 @@
       </c>
       <c r="B302" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -29611,28 +29811,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8512114742251935</v>
+        <v>-1.056166454436737</v>
       </c>
       <c r="J2" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K2" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009345301534280925</v>
+        <v>0.01411709463316668</v>
       </c>
       <c r="M2" t="n">
-        <v>54.46633971319853</v>
+        <v>55.39323963877717</v>
       </c>
       <c r="N2" t="n">
-        <v>4246.855531159767</v>
+        <v>4349.342473914885</v>
       </c>
       <c r="O2" t="n">
-        <v>65.16790261439881</v>
+        <v>65.94954491059725</v>
       </c>
       <c r="P2" t="n">
-        <v>501.117473638003</v>
+        <v>503.1741933166774</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29689,28 +29889,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.090062599292947</v>
+        <v>-1.306641547583912</v>
       </c>
       <c r="J3" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01379299805458267</v>
+        <v>0.01941837185721518</v>
       </c>
       <c r="M3" t="n">
-        <v>52.90848701158441</v>
+        <v>53.90526766115469</v>
       </c>
       <c r="N3" t="n">
-        <v>4310.569311991815</v>
+        <v>4416.443411235133</v>
       </c>
       <c r="O3" t="n">
-        <v>65.65492602990133</v>
+        <v>66.45632709708785</v>
       </c>
       <c r="P3" t="n">
-        <v>504.3182868322177</v>
+        <v>506.6449582881093</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29767,28 +29967,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6062028986087586</v>
+        <v>-0.7853635652295458</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K4" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004476186456407349</v>
+        <v>0.007446768995347464</v>
       </c>
       <c r="M4" t="n">
-        <v>52.73985917895792</v>
+        <v>53.4811516864406</v>
       </c>
       <c r="N4" t="n">
-        <v>4399.252158444514</v>
+        <v>4467.616188989044</v>
       </c>
       <c r="O4" t="n">
-        <v>66.32685849973986</v>
+        <v>66.8402288220877</v>
       </c>
       <c r="P4" t="n">
-        <v>494.4954581517227</v>
+        <v>496.3347208939094</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29845,28 +30045,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09089160217572513</v>
+        <v>-0.04075538053689329</v>
       </c>
       <c r="J5" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K5" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001211365927128449</v>
+        <v>2.439424923639244e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>48.86501418880106</v>
+        <v>49.35170995952192</v>
       </c>
       <c r="N5" t="n">
-        <v>3750.416560183296</v>
+        <v>3778.754490239888</v>
       </c>
       <c r="O5" t="n">
-        <v>61.24064467478519</v>
+        <v>61.47157465235365</v>
       </c>
       <c r="P5" t="n">
-        <v>482.7341122745097</v>
+        <v>484.0808373628298</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29923,28 +30123,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9118106067374844</v>
+        <v>0.7991905292469558</v>
       </c>
       <c r="J6" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K6" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01361387190188945</v>
+        <v>0.01051726808269582</v>
       </c>
       <c r="M6" t="n">
-        <v>44.30637017559496</v>
+        <v>44.78894405612219</v>
       </c>
       <c r="N6" t="n">
-        <v>3228.212359755425</v>
+        <v>3248.366990930324</v>
       </c>
       <c r="O6" t="n">
-        <v>56.81735966899047</v>
+        <v>56.99444701837473</v>
       </c>
       <c r="P6" t="n">
-        <v>461.8778745987543</v>
+        <v>463.0460950675664</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30001,28 +30201,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.422142026443832</v>
+        <v>1.312574090825484</v>
       </c>
       <c r="J7" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K7" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03643452439161809</v>
+        <v>0.03124126612628542</v>
       </c>
       <c r="M7" t="n">
-        <v>40.96478495541197</v>
+        <v>41.11929339760116</v>
       </c>
       <c r="N7" t="n">
-        <v>2827.624524927437</v>
+        <v>2848.291798746908</v>
       </c>
       <c r="O7" t="n">
-        <v>53.17541278567978</v>
+        <v>53.36939009157691</v>
       </c>
       <c r="P7" t="n">
-        <v>454.922612796942</v>
+        <v>456.0753177123765</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30079,28 +30279,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.336632704497955</v>
+        <v>1.252290413451993</v>
       </c>
       <c r="J8" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K8" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05595657848542179</v>
+        <v>0.04945021942207684</v>
       </c>
       <c r="M8" t="n">
-        <v>32.25847386414426</v>
+        <v>32.38506240117778</v>
       </c>
       <c r="N8" t="n">
-        <v>1611.953989750332</v>
+        <v>1625.793955800468</v>
       </c>
       <c r="O8" t="n">
-        <v>40.14914681223415</v>
+        <v>40.32113534860431</v>
       </c>
       <c r="P8" t="n">
-        <v>443.1851839775688</v>
+        <v>444.0608247322722</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30157,28 +30357,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6806552686789267</v>
+        <v>0.6271803296213271</v>
       </c>
       <c r="J9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K9" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02605965264461085</v>
+        <v>0.02231211036488889</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94763259610916</v>
+        <v>24.98855534159128</v>
       </c>
       <c r="N9" t="n">
-        <v>918.3539404923579</v>
+        <v>921.9175660686216</v>
       </c>
       <c r="O9" t="n">
-        <v>30.30435514067834</v>
+        <v>30.36309546256148</v>
       </c>
       <c r="P9" t="n">
-        <v>432.1725080140322</v>
+        <v>432.7319246341052</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30235,28 +30435,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4778935397937786</v>
+        <v>0.4548817688048726</v>
       </c>
       <c r="J10" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K10" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02517985641976095</v>
+        <v>0.02311984446544524</v>
       </c>
       <c r="M10" t="n">
-        <v>18.17568261304084</v>
+        <v>18.17111080911117</v>
       </c>
       <c r="N10" t="n">
-        <v>473.3626002243302</v>
+        <v>471.9087441668901</v>
       </c>
       <c r="O10" t="n">
-        <v>21.75689776195885</v>
+        <v>21.723460685786</v>
       </c>
       <c r="P10" t="n">
-        <v>419.3769900622649</v>
+        <v>419.6178256739698</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30313,28 +30513,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.542261933777198</v>
+        <v>0.5285364842572274</v>
       </c>
       <c r="J11" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K11" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04127100273497497</v>
+        <v>0.03979509650488766</v>
       </c>
       <c r="M11" t="n">
-        <v>15.06962752605281</v>
+        <v>15.02527525994561</v>
       </c>
       <c r="N11" t="n">
-        <v>366.5711383322845</v>
+        <v>364.7166705184528</v>
       </c>
       <c r="O11" t="n">
-        <v>19.14604759035881</v>
+        <v>19.09755666357487</v>
       </c>
       <c r="P11" t="n">
-        <v>412.3598445432814</v>
+        <v>412.5026258007948</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30391,28 +30591,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4368488334073226</v>
+        <v>0.4390112285734732</v>
       </c>
       <c r="J12" t="n">
+        <v>293</v>
+      </c>
+      <c r="K12" t="n">
         <v>291</v>
       </c>
-      <c r="K12" t="n">
-        <v>289</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.02832515243182776</v>
+        <v>0.02902391400543392</v>
       </c>
       <c r="M12" t="n">
-        <v>15.01711212905681</v>
+        <v>14.92648620445696</v>
       </c>
       <c r="N12" t="n">
-        <v>347.2798593274158</v>
+        <v>344.9129394220254</v>
       </c>
       <c r="O12" t="n">
-        <v>18.63544631414595</v>
+        <v>18.57183188115877</v>
       </c>
       <c r="P12" t="n">
-        <v>397.6703350547289</v>
+        <v>397.6477156558864</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30469,28 +30669,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2690992921068935</v>
+        <v>0.2913311828383938</v>
       </c>
       <c r="J13" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K13" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01175107292020494</v>
+        <v>0.01388251598577017</v>
       </c>
       <c r="M13" t="n">
-        <v>14.7779159981571</v>
+        <v>14.79514860464631</v>
       </c>
       <c r="N13" t="n">
-        <v>317.1209457888668</v>
+        <v>316.60109331003</v>
       </c>
       <c r="O13" t="n">
-        <v>17.8078899869936</v>
+        <v>17.79328787239812</v>
       </c>
       <c r="P13" t="n">
-        <v>391.4208979989697</v>
+        <v>391.1851049283042</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30547,28 +30747,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02885746070464317</v>
+        <v>0.07168899464111175</v>
       </c>
       <c r="J14" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K14" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001307906733565289</v>
+        <v>0.0008040005182864407</v>
       </c>
       <c r="M14" t="n">
-        <v>15.60969701118383</v>
+        <v>15.75307518689455</v>
       </c>
       <c r="N14" t="n">
-        <v>330.5530250626308</v>
+        <v>334.4600226349617</v>
       </c>
       <c r="O14" t="n">
-        <v>18.18111726662118</v>
+        <v>18.28824821121372</v>
       </c>
       <c r="P14" t="n">
-        <v>392.3610266509488</v>
+        <v>391.9064094992689</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30625,28 +30825,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.478954545993487</v>
+        <v>-0.4271054282425726</v>
       </c>
       <c r="J15" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K15" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02904640468607145</v>
+        <v>0.02306828023291074</v>
       </c>
       <c r="M15" t="n">
-        <v>16.44678196396885</v>
+        <v>16.62395601009208</v>
       </c>
       <c r="N15" t="n">
-        <v>409.5041346440559</v>
+        <v>416.0651435239566</v>
       </c>
       <c r="O15" t="n">
-        <v>20.23620850465956</v>
+        <v>20.39767495387542</v>
       </c>
       <c r="P15" t="n">
-        <v>396.5848556771869</v>
+        <v>396.0463858101998</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30703,28 +30903,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5324094433182455</v>
+        <v>-0.4644969635089</v>
       </c>
       <c r="J16" t="n">
+        <v>293</v>
+      </c>
+      <c r="K16" t="n">
         <v>291</v>
       </c>
-      <c r="K16" t="n">
-        <v>289</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.04513327571041814</v>
+        <v>0.03360750022081183</v>
       </c>
       <c r="M16" t="n">
-        <v>13.81497755238768</v>
+        <v>14.11508166341728</v>
       </c>
       <c r="N16" t="n">
-        <v>319.6019062905034</v>
+        <v>333.4426542404829</v>
       </c>
       <c r="O16" t="n">
-        <v>17.87741329976189</v>
+        <v>18.26041221441846</v>
       </c>
       <c r="P16" t="n">
-        <v>394.0257583157619</v>
+        <v>393.3185873289137</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30781,28 +30981,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6799263456471314</v>
+        <v>-0.6107185652268144</v>
       </c>
       <c r="J17" t="n">
+        <v>293</v>
+      </c>
+      <c r="K17" t="n">
         <v>291</v>
       </c>
-      <c r="K17" t="n">
-        <v>289</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.07037507858084247</v>
+        <v>0.05567086597989712</v>
       </c>
       <c r="M17" t="n">
-        <v>14.10859037688262</v>
+        <v>14.37002852350274</v>
       </c>
       <c r="N17" t="n">
-        <v>326.4014151145705</v>
+        <v>340.9847458143371</v>
       </c>
       <c r="O17" t="n">
-        <v>18.0665828289295</v>
+        <v>18.4657722777667</v>
       </c>
       <c r="P17" t="n">
-        <v>396.4526182899847</v>
+        <v>395.7320188097886</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30859,28 +31059,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9503469662451115</v>
+        <v>-0.8849006357936389</v>
       </c>
       <c r="J18" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K18" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1043135149891806</v>
+        <v>0.09000714183520664</v>
       </c>
       <c r="M18" t="n">
-        <v>16.19055085482044</v>
+        <v>16.38386359308923</v>
       </c>
       <c r="N18" t="n">
-        <v>415.352055062328</v>
+        <v>427.5795984879069</v>
       </c>
       <c r="O18" t="n">
-        <v>20.38018780733701</v>
+        <v>20.67799793229284</v>
       </c>
       <c r="P18" t="n">
-        <v>404.8329806744352</v>
+        <v>404.1533643233822</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30937,28 +31137,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7409827475826237</v>
+        <v>-0.6864475761406068</v>
       </c>
       <c r="J19" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K19" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08546440360310614</v>
+        <v>0.07303956349983098</v>
       </c>
       <c r="M19" t="n">
-        <v>13.57994462384601</v>
+        <v>13.70054928394401</v>
       </c>
       <c r="N19" t="n">
-        <v>313.5988837340555</v>
+        <v>321.8862648518921</v>
       </c>
       <c r="O19" t="n">
-        <v>17.70872337956792</v>
+        <v>17.94118905903096</v>
       </c>
       <c r="P19" t="n">
-        <v>401.8285793497511</v>
+        <v>401.2613792262123</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31015,28 +31215,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6104233799230599</v>
+        <v>-0.5662271828874441</v>
       </c>
       <c r="J20" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K20" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06180974207059886</v>
+        <v>0.0532735348846084</v>
       </c>
       <c r="M20" t="n">
-        <v>13.9073070253574</v>
+        <v>14.02599217485798</v>
       </c>
       <c r="N20" t="n">
-        <v>301.883428585651</v>
+        <v>306.6755104029374</v>
       </c>
       <c r="O20" t="n">
-        <v>17.37479290770543</v>
+        <v>17.51215322006227</v>
       </c>
       <c r="P20" t="n">
-        <v>394.1833094224989</v>
+        <v>393.7236349758729</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31093,28 +31293,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3242357071211872</v>
+        <v>-0.289260091141128</v>
       </c>
       <c r="J21" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K21" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01954922691961003</v>
+        <v>0.01562106402352603</v>
       </c>
       <c r="M21" t="n">
-        <v>13.76435427162453</v>
+        <v>13.83037883268561</v>
       </c>
       <c r="N21" t="n">
-        <v>281.4238205149983</v>
+        <v>283.8006601319427</v>
       </c>
       <c r="O21" t="n">
-        <v>16.77569135728833</v>
+        <v>16.84638418569227</v>
       </c>
       <c r="P21" t="n">
-        <v>386.888017682842</v>
+        <v>386.5242407868041</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31171,28 +31371,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2221362217533905</v>
+        <v>-0.1773874156144838</v>
       </c>
       <c r="J22" t="n">
+        <v>293</v>
+      </c>
+      <c r="K22" t="n">
         <v>291</v>
       </c>
-      <c r="K22" t="n">
-        <v>289</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.007336017442038933</v>
+        <v>0.004669522514584745</v>
       </c>
       <c r="M22" t="n">
-        <v>15.73570525945762</v>
+        <v>15.8662466142408</v>
       </c>
       <c r="N22" t="n">
-        <v>356.3346059515583</v>
+        <v>360.9310322748376</v>
       </c>
       <c r="O22" t="n">
-        <v>18.87682722153165</v>
+        <v>18.99818497317145</v>
       </c>
       <c r="P22" t="n">
-        <v>379.7365884011855</v>
+        <v>379.2698789048847</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31249,28 +31449,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>0.003395412665435605</v>
+        <v>0.05363850871641625</v>
       </c>
       <c r="J23" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K23" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L23" t="n">
-        <v>1.77372151277666e-06</v>
+        <v>0.0004379151269814363</v>
       </c>
       <c r="M23" t="n">
-        <v>15.53314410269664</v>
+        <v>15.7157376197254</v>
       </c>
       <c r="N23" t="n">
-        <v>347.3033880567482</v>
+        <v>353.8094570443091</v>
       </c>
       <c r="O23" t="n">
-        <v>18.63607759311889</v>
+        <v>18.80982341874344</v>
       </c>
       <c r="P23" t="n">
-        <v>373.3046499685412</v>
+        <v>372.7803786434636</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31327,28 +31527,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1530581736080436</v>
+        <v>0.1892332053851541</v>
       </c>
       <c r="J24" t="n">
+        <v>293</v>
+      </c>
+      <c r="K24" t="n">
         <v>291</v>
       </c>
-      <c r="K24" t="n">
-        <v>289</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.003750839915765414</v>
+        <v>0.005729582220491802</v>
       </c>
       <c r="M24" t="n">
-        <v>15.27721735769845</v>
+        <v>15.34353540760709</v>
       </c>
       <c r="N24" t="n">
-        <v>333.5129936200074</v>
+        <v>335.8453369930895</v>
       </c>
       <c r="O24" t="n">
-        <v>18.26233812029575</v>
+        <v>18.32608351484543</v>
       </c>
       <c r="P24" t="n">
-        <v>368.2975603961924</v>
+        <v>367.9214523868371</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31405,28 +31605,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2897116228683274</v>
+        <v>0.310848893572313</v>
       </c>
       <c r="J25" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K25" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01546540919654382</v>
+        <v>0.01793266487434031</v>
       </c>
       <c r="M25" t="n">
-        <v>14.29478981212105</v>
+        <v>14.29923288015861</v>
       </c>
       <c r="N25" t="n">
-        <v>286.0318198271528</v>
+        <v>285.6479106250749</v>
       </c>
       <c r="O25" t="n">
-        <v>16.91247527203374</v>
+        <v>16.90112157890934</v>
       </c>
       <c r="P25" t="n">
-        <v>370.1676848745631</v>
+        <v>369.9480269536804</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31483,28 +31683,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3698924016737358</v>
+        <v>0.3747361453827108</v>
       </c>
       <c r="J26" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K26" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02158505095474383</v>
+        <v>0.02247062654000209</v>
       </c>
       <c r="M26" t="n">
-        <v>15.26514757428981</v>
+        <v>15.18020898178484</v>
       </c>
       <c r="N26" t="n">
-        <v>331.1954966185256</v>
+        <v>329.0091408261314</v>
       </c>
       <c r="O26" t="n">
-        <v>18.19877733856111</v>
+        <v>18.13860912049574</v>
       </c>
       <c r="P26" t="n">
-        <v>365.6680086035919</v>
+        <v>365.6177066817805</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31561,28 +31761,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2742816809251358</v>
+        <v>0.2680896858235511</v>
       </c>
       <c r="J27" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K27" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01242437290547782</v>
+        <v>0.01205260754337878</v>
       </c>
       <c r="M27" t="n">
-        <v>15.19115949284535</v>
+        <v>15.11779823451151</v>
       </c>
       <c r="N27" t="n">
-        <v>319.3398311544977</v>
+        <v>317.2891160278742</v>
       </c>
       <c r="O27" t="n">
-        <v>17.87008201308818</v>
+        <v>17.81261115131283</v>
       </c>
       <c r="P27" t="n">
-        <v>362.4081527464047</v>
+        <v>362.4724627798121</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31620,7 +31820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB292"/>
+  <dimension ref="A1:AB294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72379,6 +72579,290 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-37.797696911828865,174.84164619573195</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>-37.79711418705076,174.84112664300886</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>-37.79669645527578,174.8403623850236</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-37.79637125062684,174.83946089182234</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-37.79587421874122,174.83880857270714</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-37.79537001986636,174.83816384171791</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-37.79482985064218,174.83757957449023</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-37.79419619054137,174.8370222877974</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-37.79349021139601,174.83655922581087</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-37.79278021496386,174.83626902521857</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-37.792064037313125,174.83607230734452</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-37.7913253387298,174.83584820128377</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-37.7905916724078,174.83566890115537</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-37.7898785175699,174.83563104741222</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-37.78916830062618,174.83548562002514</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-37.78845507071004,174.83544936127618</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-37.78775465509911,174.83541765767393</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>-37.78706679300128,174.83540515813726</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>-37.78636078625694,174.83543402226053</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>-37.78564784561865,174.8353950751618</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>-37.78494450374802,174.83525259520152</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>-37.78424159527356,174.83510637204418</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>-37.78352381293288,174.83512272730553</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>-37.78282281608289,174.83507735032418</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>-37.78211134876623,174.83506456342616</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>-37.78139002837172,174.8350472504786</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-37.79769475308156,174.84164939733756</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>-37.79712865643162,174.8411051836915</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>-37.79671063283641,174.84034135835574</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-37.796373234301555,174.83945794981275</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-37.795880586127055,174.83879900091017</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-37.79537294369501,174.8381593742344</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-37.79482424162832,174.83758816868362</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-37.794191450058065,174.8370316757445</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-37.79348650834712,174.83657117764662</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-37.792774897197845,174.83629048483323</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-37.79206069024429,174.8360881040328</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-37.79132641771791,174.8358393351901</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-37.79059169556882,174.83566856178822</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-37.789879238179175,174.83561972989708</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-37.78916842383143,174.83548335458332</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-37.78845575179744,174.8354356501724</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-37.787755149892114,174.83540962079343</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>-37.7870665088053,174.8354082025816</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>-37.78636279839564,174.83541626404968</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>-37.78565076386943,174.83536922290827</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>-37.78494755343081,174.83522447369847</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>-37.7842442756651,174.8350807084206</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>-37.7835257644514,174.83510404256847</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>-37.78282452177636,174.83506435761436</t>
+        </is>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>-37.7821105362094,174.83506968432908</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>-37.78138769301598,174.83506194417524</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB294"/>
+  <dimension ref="A1:AB295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26589,6 +26589,96 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="C295" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="D295" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="E295" t="n">
+        <v>396.78</v>
+      </c>
+      <c r="F295" t="n">
+        <v>405.36</v>
+      </c>
+      <c r="G295" t="n">
+        <v>412.44</v>
+      </c>
+      <c r="H295" t="n">
+        <v>412.18</v>
+      </c>
+      <c r="I295" t="n">
+        <v>401.12</v>
+      </c>
+      <c r="J295" t="n">
+        <v>404.74</v>
+      </c>
+      <c r="K295" t="n">
+        <v>406.47</v>
+      </c>
+      <c r="L295" t="n">
+        <v>404.09</v>
+      </c>
+      <c r="M295" t="n">
+        <v>413.92</v>
+      </c>
+      <c r="N295" t="n">
+        <v>419.82</v>
+      </c>
+      <c r="O295" t="n">
+        <v>426.01</v>
+      </c>
+      <c r="P295" t="n">
+        <v>430</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>432.66</v>
+      </c>
+      <c r="R295" t="n">
+        <v>429</v>
+      </c>
+      <c r="S295" t="n">
+        <v>421.78</v>
+      </c>
+      <c r="T295" t="n">
+        <v>410.99</v>
+      </c>
+      <c r="U295" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="V295" t="n">
+        <v>409.89</v>
+      </c>
+      <c r="W295" t="n">
+        <v>413.45</v>
+      </c>
+      <c r="X295" t="n">
+        <v>406.79</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>395</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>357.42</v>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26600,7 +26690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B304"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29643,6 +29733,16 @@
       </c>
       <c r="B304" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -29811,28 +29911,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.056166454436737</v>
+        <v>-1.159144708299404</v>
       </c>
       <c r="J2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01411709463316668</v>
+        <v>0.01683684348774361</v>
       </c>
       <c r="M2" t="n">
-        <v>55.39323963877717</v>
+        <v>55.85804464521907</v>
       </c>
       <c r="N2" t="n">
-        <v>4349.342473914885</v>
+        <v>4401.74735775783</v>
       </c>
       <c r="O2" t="n">
-        <v>65.94954491059725</v>
+        <v>66.34566570438366</v>
       </c>
       <c r="P2" t="n">
-        <v>503.1741933166774</v>
+        <v>504.2130251854453</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29889,28 +29989,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.306641547583912</v>
+        <v>-1.413022293677642</v>
       </c>
       <c r="J3" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01941837185721518</v>
+        <v>0.02248766425460413</v>
       </c>
       <c r="M3" t="n">
-        <v>53.90526766115469</v>
+        <v>54.38982487781404</v>
       </c>
       <c r="N3" t="n">
-        <v>4416.443411235133</v>
+        <v>4467.353833235314</v>
       </c>
       <c r="O3" t="n">
-        <v>66.45632709708785</v>
+        <v>66.83826623451056</v>
       </c>
       <c r="P3" t="n">
-        <v>506.6449582881093</v>
+        <v>507.7934669381846</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29967,28 +30067,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7853635652295458</v>
+        <v>-0.8707908418011469</v>
       </c>
       <c r="J4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K4" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007446768995347464</v>
+        <v>0.009122133332004623</v>
       </c>
       <c r="M4" t="n">
-        <v>53.4811516864406</v>
+        <v>53.84298565494998</v>
       </c>
       <c r="N4" t="n">
-        <v>4467.616188989044</v>
+        <v>4497.538493788015</v>
       </c>
       <c r="O4" t="n">
-        <v>66.8402288220877</v>
+        <v>67.06368983129407</v>
       </c>
       <c r="P4" t="n">
-        <v>496.3347208939094</v>
+        <v>497.2162600881205</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30045,28 +30145,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04075538053689329</v>
+        <v>-0.1056427780681919</v>
       </c>
       <c r="J5" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>2.439424923639244e-05</v>
+        <v>0.0001640346477733701</v>
       </c>
       <c r="M5" t="n">
-        <v>49.35170995952192</v>
+        <v>49.58690651565755</v>
       </c>
       <c r="N5" t="n">
-        <v>3778.754490239888</v>
+        <v>3792.364747423058</v>
       </c>
       <c r="O5" t="n">
-        <v>61.47157465235365</v>
+        <v>61.58217881354198</v>
       </c>
       <c r="P5" t="n">
-        <v>484.0808373628298</v>
+        <v>484.7482269410615</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30123,28 +30223,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7991905292469558</v>
+        <v>0.7429469282137309</v>
       </c>
       <c r="J6" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K6" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01051726808269582</v>
+        <v>0.009113107963439893</v>
       </c>
       <c r="M6" t="n">
-        <v>44.78894405612219</v>
+        <v>45.02535618473546</v>
       </c>
       <c r="N6" t="n">
-        <v>3248.366990930324</v>
+        <v>3258.551663153341</v>
       </c>
       <c r="O6" t="n">
-        <v>56.99444701837473</v>
+        <v>57.08372502870973</v>
       </c>
       <c r="P6" t="n">
-        <v>463.0460950675664</v>
+        <v>463.6325711942634</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30201,28 +30301,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.312574090825484</v>
+        <v>1.256673834958872</v>
       </c>
       <c r="J7" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K7" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03124126612628542</v>
+        <v>0.02871991614545721</v>
       </c>
       <c r="M7" t="n">
-        <v>41.11929339760116</v>
+        <v>41.20228262141242</v>
       </c>
       <c r="N7" t="n">
-        <v>2848.291798746908</v>
+        <v>2859.600617277566</v>
       </c>
       <c r="O7" t="n">
-        <v>53.36939009157691</v>
+        <v>53.47523368137409</v>
       </c>
       <c r="P7" t="n">
-        <v>456.0753177123765</v>
+        <v>456.6664887353305</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30279,28 +30379,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.252290413451993</v>
+        <v>1.207396983285496</v>
       </c>
       <c r="J8" t="n">
+        <v>294</v>
+      </c>
+      <c r="K8" t="n">
         <v>293</v>
       </c>
-      <c r="K8" t="n">
-        <v>292</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04945021942207684</v>
+        <v>0.04608148978943727</v>
       </c>
       <c r="M8" t="n">
-        <v>32.38506240117778</v>
+        <v>32.46502390300127</v>
       </c>
       <c r="N8" t="n">
-        <v>1625.793955800468</v>
+        <v>1634.453749266364</v>
       </c>
       <c r="O8" t="n">
-        <v>40.32113534860431</v>
+        <v>40.42837801923748</v>
       </c>
       <c r="P8" t="n">
-        <v>444.0608247322722</v>
+        <v>444.5293351095081</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30357,28 +30457,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6271803296213271</v>
+        <v>0.5935817547960507</v>
       </c>
       <c r="J9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02231211036488889</v>
+        <v>0.02001525817358185</v>
       </c>
       <c r="M9" t="n">
-        <v>24.98855534159128</v>
+        <v>25.0378619869525</v>
       </c>
       <c r="N9" t="n">
-        <v>921.9175660686216</v>
+        <v>926.6236077778186</v>
       </c>
       <c r="O9" t="n">
-        <v>30.36309546256148</v>
+        <v>30.4404928964335</v>
       </c>
       <c r="P9" t="n">
-        <v>432.7319246341052</v>
+        <v>433.085233047496</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30435,28 +30535,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4548817688048726</v>
+        <v>0.4361337755992172</v>
       </c>
       <c r="J10" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02311984446544524</v>
+        <v>0.02134131388039051</v>
       </c>
       <c r="M10" t="n">
-        <v>18.17111080911117</v>
+        <v>18.2070378808032</v>
       </c>
       <c r="N10" t="n">
-        <v>471.9087441668901</v>
+        <v>472.7543259940567</v>
       </c>
       <c r="O10" t="n">
-        <v>21.723460685786</v>
+        <v>21.74291438593402</v>
       </c>
       <c r="P10" t="n">
-        <v>419.6178256739698</v>
+        <v>419.815080387635</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30513,28 +30613,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5285364842572274</v>
+        <v>0.5147628735580013</v>
       </c>
       <c r="J11" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K11" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03979509650488766</v>
+        <v>0.03796655778054925</v>
       </c>
       <c r="M11" t="n">
-        <v>15.02527525994561</v>
+        <v>15.03253621452417</v>
       </c>
       <c r="N11" t="n">
-        <v>364.7166705184528</v>
+        <v>364.8167745163714</v>
       </c>
       <c r="O11" t="n">
-        <v>19.09755666357487</v>
+        <v>19.1001773425372</v>
       </c>
       <c r="P11" t="n">
-        <v>412.5026258007948</v>
+        <v>412.6466580944548</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30591,28 +30691,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4390112285734732</v>
+        <v>0.4354502532928227</v>
       </c>
       <c r="J12" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K12" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02902391400543392</v>
+        <v>0.02877390061824003</v>
       </c>
       <c r="M12" t="n">
-        <v>14.92648620445696</v>
+        <v>14.88965012328876</v>
       </c>
       <c r="N12" t="n">
-        <v>344.9129394220254</v>
+        <v>343.8205700591661</v>
       </c>
       <c r="O12" t="n">
-        <v>18.57183188115877</v>
+        <v>18.54239925304075</v>
       </c>
       <c r="P12" t="n">
-        <v>397.6477156558864</v>
+        <v>397.6851667147391</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30669,28 +30769,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2913311828383938</v>
+        <v>0.3019777961708424</v>
       </c>
       <c r="J13" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K13" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01388251598577017</v>
+        <v>0.01497755503644416</v>
       </c>
       <c r="M13" t="n">
-        <v>14.79514860464631</v>
+        <v>14.80052049587557</v>
       </c>
       <c r="N13" t="n">
-        <v>316.60109331003</v>
+        <v>316.2830140880556</v>
       </c>
       <c r="O13" t="n">
-        <v>17.79328787239812</v>
+        <v>17.78434744622517</v>
       </c>
       <c r="P13" t="n">
-        <v>391.1851049283042</v>
+        <v>391.0716086838353</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30747,28 +30847,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07168899464111175</v>
+        <v>0.09009381201089527</v>
       </c>
       <c r="J14" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K14" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0008040005182864407</v>
+        <v>0.001270270521861905</v>
       </c>
       <c r="M14" t="n">
-        <v>15.75307518689455</v>
+        <v>15.80527556815294</v>
       </c>
       <c r="N14" t="n">
-        <v>334.4600226349617</v>
+        <v>335.6130587352362</v>
       </c>
       <c r="O14" t="n">
-        <v>18.28824821121372</v>
+        <v>18.31974505104359</v>
       </c>
       <c r="P14" t="n">
-        <v>391.9064094992689</v>
+        <v>391.7100636228641</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30825,28 +30925,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4271054282425726</v>
+        <v>-0.3985298708078454</v>
       </c>
       <c r="J15" t="n">
+        <v>294</v>
+      </c>
+      <c r="K15" t="n">
         <v>293</v>
       </c>
-      <c r="K15" t="n">
-        <v>292</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.02306828023291074</v>
+        <v>0.02002558167500801</v>
       </c>
       <c r="M15" t="n">
-        <v>16.62395601009208</v>
+        <v>16.73054207977808</v>
       </c>
       <c r="N15" t="n">
-        <v>416.0651435239566</v>
+        <v>420.3790396344438</v>
       </c>
       <c r="O15" t="n">
-        <v>20.39767495387542</v>
+        <v>20.5031470665955</v>
       </c>
       <c r="P15" t="n">
-        <v>396.0463858101998</v>
+        <v>395.7480791434305</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30903,28 +31003,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4644969635089</v>
+        <v>-0.4304894885683343</v>
       </c>
       <c r="J16" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K16" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03360750022081183</v>
+        <v>0.02854491200681253</v>
       </c>
       <c r="M16" t="n">
-        <v>14.11508166341728</v>
+        <v>14.2673540070675</v>
       </c>
       <c r="N16" t="n">
-        <v>333.4426542404829</v>
+        <v>340.4071281730144</v>
       </c>
       <c r="O16" t="n">
-        <v>18.26041221441846</v>
+        <v>18.45012542431661</v>
       </c>
       <c r="P16" t="n">
-        <v>393.3185873289137</v>
+        <v>392.962626483499</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30981,28 +31081,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6107185652268144</v>
+        <v>-0.57404740297072</v>
       </c>
       <c r="J17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K17" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05567086597989712</v>
+        <v>0.04857370299664987</v>
       </c>
       <c r="M17" t="n">
-        <v>14.37002852350274</v>
+        <v>14.5142342975085</v>
       </c>
       <c r="N17" t="n">
-        <v>340.9847458143371</v>
+        <v>349.3369518143527</v>
       </c>
       <c r="O17" t="n">
-        <v>18.4657722777667</v>
+        <v>18.6905578251253</v>
       </c>
       <c r="P17" t="n">
-        <v>395.7320188097886</v>
+        <v>395.3481958070145</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31059,28 +31159,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8849006357936389</v>
+        <v>-0.851674033889908</v>
       </c>
       <c r="J18" t="n">
+        <v>294</v>
+      </c>
+      <c r="K18" t="n">
         <v>293</v>
       </c>
-      <c r="K18" t="n">
-        <v>292</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.09000714183520664</v>
+        <v>0.08312088572079479</v>
       </c>
       <c r="M18" t="n">
-        <v>16.38386359308923</v>
+        <v>16.48224352151805</v>
       </c>
       <c r="N18" t="n">
-        <v>427.5795984879069</v>
+        <v>433.9498782292302</v>
       </c>
       <c r="O18" t="n">
-        <v>20.67799793229284</v>
+        <v>20.83146366027194</v>
       </c>
       <c r="P18" t="n">
-        <v>404.1533643233822</v>
+        <v>403.8065234903734</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31137,28 +31237,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6864475761406068</v>
+        <v>-0.6598098135843611</v>
       </c>
       <c r="J19" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K19" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07303956349983098</v>
+        <v>0.06736074813737258</v>
       </c>
       <c r="M19" t="n">
-        <v>13.70054928394401</v>
+        <v>13.76019240760347</v>
       </c>
       <c r="N19" t="n">
-        <v>321.8862648518921</v>
+        <v>325.8056259280597</v>
       </c>
       <c r="O19" t="n">
-        <v>17.94118905903096</v>
+        <v>18.05008659059728</v>
       </c>
       <c r="P19" t="n">
-        <v>401.2613792262123</v>
+        <v>400.9828865693177</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31215,28 +31315,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5662271828874441</v>
+        <v>-0.5440199599740158</v>
       </c>
       <c r="J20" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K20" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0532735348846084</v>
+        <v>0.04920480656417969</v>
       </c>
       <c r="M20" t="n">
-        <v>14.02599217485798</v>
+        <v>14.08461132423787</v>
       </c>
       <c r="N20" t="n">
-        <v>306.6755104029374</v>
+        <v>309.1173398828584</v>
       </c>
       <c r="O20" t="n">
-        <v>17.51215322006227</v>
+        <v>17.58173313080535</v>
       </c>
       <c r="P20" t="n">
-        <v>393.7236349758729</v>
+        <v>393.4914627542626</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31293,28 +31393,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.289260091141128</v>
+        <v>-0.2696746465176035</v>
       </c>
       <c r="J21" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K21" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01562106402352603</v>
+        <v>0.01357939842504141</v>
       </c>
       <c r="M21" t="n">
-        <v>13.83037883268561</v>
+        <v>13.87467866584777</v>
       </c>
       <c r="N21" t="n">
-        <v>283.8006601319427</v>
+        <v>285.5460058717599</v>
       </c>
       <c r="O21" t="n">
-        <v>16.84638418569227</v>
+        <v>16.89810657652981</v>
       </c>
       <c r="P21" t="n">
-        <v>386.5242407868041</v>
+        <v>386.3194787502723</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31371,28 +31471,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1773874156144838</v>
+        <v>-0.1529728101781225</v>
       </c>
       <c r="J22" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K22" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004669522514584745</v>
+        <v>0.003462724122472616</v>
       </c>
       <c r="M22" t="n">
-        <v>15.8662466142408</v>
+        <v>15.94207134783232</v>
       </c>
       <c r="N22" t="n">
-        <v>360.9310322748376</v>
+        <v>363.9151885578813</v>
       </c>
       <c r="O22" t="n">
-        <v>18.99818497317145</v>
+        <v>19.07656123513568</v>
       </c>
       <c r="P22" t="n">
-        <v>379.2698789048847</v>
+        <v>379.0139161775402</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31449,28 +31549,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05363850871641625</v>
+        <v>0.08080239569447664</v>
       </c>
       <c r="J23" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K23" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0004379151269814363</v>
+        <v>0.0009861424284988152</v>
       </c>
       <c r="M23" t="n">
-        <v>15.7157376197254</v>
+        <v>15.81796472287114</v>
       </c>
       <c r="N23" t="n">
-        <v>353.8094570443091</v>
+        <v>357.8316753128159</v>
       </c>
       <c r="O23" t="n">
-        <v>18.80982341874344</v>
+        <v>18.9164392873716</v>
       </c>
       <c r="P23" t="n">
-        <v>372.7803786434636</v>
+        <v>372.4954441362569</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31527,28 +31627,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1892332053851541</v>
+        <v>0.2126084023805689</v>
       </c>
       <c r="J24" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K24" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L24" t="n">
-        <v>0.005729582220491802</v>
+        <v>0.007193397119558242</v>
       </c>
       <c r="M24" t="n">
-        <v>15.34353540760709</v>
+        <v>15.40107166655839</v>
       </c>
       <c r="N24" t="n">
-        <v>335.8453369930895</v>
+        <v>338.582767712936</v>
       </c>
       <c r="O24" t="n">
-        <v>18.32608351484543</v>
+        <v>18.40061867745039</v>
       </c>
       <c r="P24" t="n">
-        <v>367.9214523868371</v>
+        <v>367.6771483455974</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31605,28 +31705,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.310848893572313</v>
+        <v>0.3224809843003908</v>
       </c>
       <c r="J25" t="n">
+        <v>294</v>
+      </c>
+      <c r="K25" t="n">
         <v>293</v>
       </c>
-      <c r="K25" t="n">
-        <v>292</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01793266487434031</v>
+        <v>0.01935388856126918</v>
       </c>
       <c r="M25" t="n">
-        <v>14.29923288015861</v>
+        <v>14.30595652618484</v>
       </c>
       <c r="N25" t="n">
-        <v>285.6479106250749</v>
+        <v>285.633116514706</v>
       </c>
       <c r="O25" t="n">
-        <v>16.90112157890934</v>
+        <v>16.90068390671532</v>
       </c>
       <c r="P25" t="n">
-        <v>369.9480269536804</v>
+        <v>369.826515797594</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31683,28 +31783,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3747361453827108</v>
+        <v>0.3749351889332069</v>
       </c>
       <c r="J26" t="n">
+        <v>294</v>
+      </c>
+      <c r="K26" t="n">
         <v>293</v>
       </c>
-      <c r="K26" t="n">
-        <v>292</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.02247062654000209</v>
+        <v>0.0226632795168995</v>
       </c>
       <c r="M26" t="n">
-        <v>15.18020898178484</v>
+        <v>15.12919251754491</v>
       </c>
       <c r="N26" t="n">
-        <v>329.0091408261314</v>
+        <v>327.8865209351009</v>
       </c>
       <c r="O26" t="n">
-        <v>18.13860912049574</v>
+        <v>18.10763708867341</v>
       </c>
       <c r="P26" t="n">
-        <v>365.6177066817805</v>
+        <v>365.6156288214194</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31761,28 +31861,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2680896858235511</v>
+        <v>0.259687311797831</v>
       </c>
       <c r="J27" t="n">
+        <v>294</v>
+      </c>
+      <c r="K27" t="n">
         <v>293</v>
       </c>
-      <c r="K27" t="n">
-        <v>292</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01205260754337878</v>
+        <v>0.01138589552684088</v>
       </c>
       <c r="M27" t="n">
-        <v>15.11779823451151</v>
+        <v>15.10920590806998</v>
       </c>
       <c r="N27" t="n">
-        <v>317.2891160278742</v>
+        <v>316.7019714732708</v>
       </c>
       <c r="O27" t="n">
-        <v>17.81261115131283</v>
+        <v>17.79612237183344</v>
       </c>
       <c r="P27" t="n">
-        <v>362.4724627798121</v>
+        <v>362.5601770508035</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31820,7 +31920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB294"/>
+  <dimension ref="A1:AB295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72863,6 +72963,148 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>-37.797670540099375,174.84168530722528</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>-37.797114128706475,174.84112672953833</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>-37.79671722569258,174.84033158051975</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-37.796366583156626,174.83946781419712</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-37.795867967125325,174.83881797046982</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-37.79535345150113,174.83818915745113</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-37.794797741891436,174.83762877184478</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-37.79414254564246,174.83712852480105</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-37.79345334470604,174.83667821527084</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-37.792750242050715,174.83638997936822</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-37.79204704626855,174.83615249746182</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-37.79132548896869,174.8358469667644</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-37.79058891623936,174.8357092858425</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-37.78988219266588,174.83557332808215</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-37.78916903369678,174.83547214064612</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-37.78845767121701,174.8353970097873</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>-37.78775606281865,174.8353947921826</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>-37.7870665088053,174.8354082025816</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>-37.78636279839564,174.83541626404968</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>-37.78565382168271,174.83534213424016</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>-37.78495045672265,174.83519770202514</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>-37.78424734400124,174.8350513303226</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>-37.78353449922411,174.83502041147298</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>-37.7828264774404,174.8350494607997</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>-37.78210550188505,174.83510141165993</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>-37.781375202370455,174.83514053317214</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB295"/>
+  <dimension ref="A1:AB297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26602,16 +26602,16 @@
         <v>337.57</v>
       </c>
       <c r="D295" t="n">
-        <v>363.21</v>
+        <v>373.77</v>
       </c>
       <c r="E295" t="n">
-        <v>396.78</v>
+        <v>406.07</v>
       </c>
       <c r="F295" t="n">
-        <v>405.36</v>
+        <v>415.25</v>
       </c>
       <c r="G295" t="n">
-        <v>412.44</v>
+        <v>419.35</v>
       </c>
       <c r="H295" t="n">
         <v>412.18</v>
@@ -26644,10 +26644,10 @@
         <v>432.66</v>
       </c>
       <c r="R295" t="n">
-        <v>429</v>
+        <v>434.75</v>
       </c>
       <c r="S295" t="n">
-        <v>421.78</v>
+        <v>429.77</v>
       </c>
       <c r="T295" t="n">
         <v>410.99</v>
@@ -26671,11 +26671,191 @@
         <v>375.78</v>
       </c>
       <c r="AA295" t="n">
-        <v>357.42</v>
+        <v>362.74</v>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="C296" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="D296" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="E296" t="n">
+        <v>415.56</v>
+      </c>
+      <c r="F296" t="n">
+        <v>421.55</v>
+      </c>
+      <c r="G296" t="n">
+        <v>422.38</v>
+      </c>
+      <c r="H296" t="n">
+        <v>413.23</v>
+      </c>
+      <c r="I296" t="n">
+        <v>400.15</v>
+      </c>
+      <c r="J296" t="n">
+        <v>401.46</v>
+      </c>
+      <c r="K296" t="n">
+        <v>403.69</v>
+      </c>
+      <c r="L296" t="n">
+        <v>403.11</v>
+      </c>
+      <c r="M296" t="n">
+        <v>414.22</v>
+      </c>
+      <c r="N296" t="n">
+        <v>422.12</v>
+      </c>
+      <c r="O296" t="n">
+        <v>426.77</v>
+      </c>
+      <c r="P296" t="n">
+        <v>432.45</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>433.81</v>
+      </c>
+      <c r="R296" t="n">
+        <v>436.22</v>
+      </c>
+      <c r="S296" t="n">
+        <v>432.38</v>
+      </c>
+      <c r="T296" t="n">
+        <v>415.79</v>
+      </c>
+      <c r="U296" t="n">
+        <v>414.54</v>
+      </c>
+      <c r="V296" t="n">
+        <v>417.23</v>
+      </c>
+      <c r="W296" t="n">
+        <v>422.62</v>
+      </c>
+      <c r="X296" t="n">
+        <v>411.83</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>397.24</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>367.53</v>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="C297" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="D297" t="n">
+        <v>396.87</v>
+      </c>
+      <c r="E297" t="n">
+        <v>426.06</v>
+      </c>
+      <c r="F297" t="n">
+        <v>430.27</v>
+      </c>
+      <c r="G297" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="H297" t="n">
+        <v>415.57</v>
+      </c>
+      <c r="I297" t="n">
+        <v>396.99</v>
+      </c>
+      <c r="J297" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="K297" t="n">
+        <v>399.58</v>
+      </c>
+      <c r="L297" t="n">
+        <v>400.55</v>
+      </c>
+      <c r="M297" t="n">
+        <v>413.54</v>
+      </c>
+      <c r="N297" t="n">
+        <v>424.01</v>
+      </c>
+      <c r="O297" t="n">
+        <v>429.09</v>
+      </c>
+      <c r="P297" t="n">
+        <v>433.91</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>436.74</v>
+      </c>
+      <c r="R297" t="n">
+        <v>439.45</v>
+      </c>
+      <c r="S297" t="n">
+        <v>435.73</v>
+      </c>
+      <c r="T297" t="n">
+        <v>422.41</v>
+      </c>
+      <c r="U297" t="n">
+        <v>420.73</v>
+      </c>
+      <c r="V297" t="n">
+        <v>422.18</v>
+      </c>
+      <c r="W297" t="n">
+        <v>426.17</v>
+      </c>
+      <c r="X297" t="n">
+        <v>411.91</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>398.62</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26690,7 +26870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29743,6 +29923,26 @@
       </c>
       <c r="B305" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -29911,28 +30111,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.159144708299404</v>
+        <v>-1.362050930616238</v>
       </c>
       <c r="J2" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K2" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01683684348774361</v>
+        <v>0.02279813195732761</v>
       </c>
       <c r="M2" t="n">
-        <v>55.85804464521907</v>
+        <v>56.75747399850619</v>
       </c>
       <c r="N2" t="n">
-        <v>4401.74735775783</v>
+        <v>4504.250204456939</v>
       </c>
       <c r="O2" t="n">
-        <v>66.34566570438366</v>
+        <v>67.11371100197738</v>
       </c>
       <c r="P2" t="n">
-        <v>504.2130251854453</v>
+        <v>506.2676769927519</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29989,28 +30189,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.413022293677642</v>
+        <v>-1.619674426484752</v>
       </c>
       <c r="J3" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02248766425460413</v>
+        <v>0.02900799773787044</v>
       </c>
       <c r="M3" t="n">
-        <v>54.38982487781404</v>
+        <v>55.38010334198445</v>
       </c>
       <c r="N3" t="n">
-        <v>4467.353833235314</v>
+        <v>4563.086826393947</v>
       </c>
       <c r="O3" t="n">
-        <v>66.83826623451056</v>
+        <v>67.55062417471764</v>
       </c>
       <c r="P3" t="n">
-        <v>507.7934669381846</v>
+        <v>510.0324867899444</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30067,28 +30267,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8707908418011469</v>
+        <v>-0.9881007836160862</v>
       </c>
       <c r="J4" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K4" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009122133332004623</v>
+        <v>0.01180001307693601</v>
       </c>
       <c r="M4" t="n">
-        <v>53.84298565494998</v>
+        <v>54.22038349000984</v>
       </c>
       <c r="N4" t="n">
-        <v>4497.538493788015</v>
+        <v>4507.089487975888</v>
       </c>
       <c r="O4" t="n">
-        <v>67.06368983129407</v>
+        <v>67.13486045249434</v>
       </c>
       <c r="P4" t="n">
-        <v>497.2162600881205</v>
+        <v>498.4315201672937</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30145,28 +30345,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1056427780681919</v>
+        <v>-0.1893542057072193</v>
       </c>
       <c r="J5" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K5" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001640346477733701</v>
+        <v>0.000532434611560606</v>
       </c>
       <c r="M5" t="n">
-        <v>49.58690651565755</v>
+        <v>49.75771497201286</v>
       </c>
       <c r="N5" t="n">
-        <v>3792.364747423058</v>
+        <v>3785.923820089566</v>
       </c>
       <c r="O5" t="n">
-        <v>61.58217881354198</v>
+        <v>61.5298612064871</v>
       </c>
       <c r="P5" t="n">
-        <v>484.7482269410615</v>
+        <v>485.6127863794122</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30223,28 +30423,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7429469282137309</v>
+        <v>0.6691249484044222</v>
       </c>
       <c r="J6" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K6" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009113107963439893</v>
+        <v>0.007480353521815086</v>
       </c>
       <c r="M6" t="n">
-        <v>45.02535618473546</v>
+        <v>45.22365247637875</v>
       </c>
       <c r="N6" t="n">
-        <v>3258.551663153341</v>
+        <v>3253.41488257526</v>
       </c>
       <c r="O6" t="n">
-        <v>57.08372502870973</v>
+        <v>57.03871389306793</v>
       </c>
       <c r="P6" t="n">
-        <v>463.6325711942634</v>
+        <v>464.4054532350663</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30301,28 +30501,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.256673834958872</v>
+        <v>1.170780039465304</v>
       </c>
       <c r="J7" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K7" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02871991614545721</v>
+        <v>0.02518770055329733</v>
       </c>
       <c r="M7" t="n">
-        <v>41.20228262141242</v>
+        <v>41.2738082293768</v>
       </c>
       <c r="N7" t="n">
-        <v>2859.600617277566</v>
+        <v>2864.541584045893</v>
       </c>
       <c r="O7" t="n">
-        <v>53.47523368137409</v>
+        <v>53.52141238836932</v>
       </c>
       <c r="P7" t="n">
-        <v>456.6664887353305</v>
+        <v>457.578415499064</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30379,28 +30579,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.207396983285496</v>
+        <v>1.122727432577356</v>
       </c>
       <c r="J8" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K8" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04608148978943727</v>
+        <v>0.04007995515846419</v>
       </c>
       <c r="M8" t="n">
-        <v>32.46502390300127</v>
+        <v>32.6087171884943</v>
       </c>
       <c r="N8" t="n">
-        <v>1634.453749266364</v>
+        <v>1648.917842706072</v>
       </c>
       <c r="O8" t="n">
-        <v>40.42837801923748</v>
+        <v>40.60686940292334</v>
       </c>
       <c r="P8" t="n">
-        <v>444.5293351095081</v>
+        <v>445.4162416130805</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30457,28 +30657,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5935817547960507</v>
+        <v>0.5244720833262663</v>
       </c>
       <c r="J9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02001525817358185</v>
+        <v>0.01565026562868355</v>
       </c>
       <c r="M9" t="n">
-        <v>25.0378619869525</v>
+        <v>25.15059170879113</v>
       </c>
       <c r="N9" t="n">
-        <v>926.6236077778186</v>
+        <v>937.1448425344421</v>
       </c>
       <c r="O9" t="n">
-        <v>30.4404928964335</v>
+        <v>30.61282153827775</v>
       </c>
       <c r="P9" t="n">
-        <v>433.085233047496</v>
+        <v>433.8146933625634</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30535,28 +30735,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4361337755992172</v>
+        <v>0.3898730864770262</v>
       </c>
       <c r="J10" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02134131388039051</v>
+        <v>0.017105845007373</v>
       </c>
       <c r="M10" t="n">
-        <v>18.2070378808032</v>
+        <v>18.32494425537778</v>
       </c>
       <c r="N10" t="n">
-        <v>472.7543259940567</v>
+        <v>477.2388459047399</v>
       </c>
       <c r="O10" t="n">
-        <v>21.74291438593402</v>
+        <v>21.84579698488339</v>
       </c>
       <c r="P10" t="n">
-        <v>419.815080387635</v>
+        <v>420.3037210510379</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30613,28 +30813,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5147628735580013</v>
+        <v>0.481238313098035</v>
       </c>
       <c r="J11" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K11" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03796655778054925</v>
+        <v>0.03346773031349759</v>
       </c>
       <c r="M11" t="n">
-        <v>15.03253621452417</v>
+        <v>15.07933850834921</v>
       </c>
       <c r="N11" t="n">
-        <v>364.8167745163714</v>
+        <v>366.4041653867354</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1001773425372</v>
+        <v>19.1416865867858</v>
       </c>
       <c r="P11" t="n">
-        <v>412.6466580944548</v>
+        <v>412.998585996187</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30691,28 +30891,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4354502532928227</v>
+        <v>0.4253438591259873</v>
       </c>
       <c r="J12" t="n">
+        <v>296</v>
+      </c>
+      <c r="K12" t="n">
         <v>294</v>
       </c>
-      <c r="K12" t="n">
-        <v>292</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.02877390061824003</v>
+        <v>0.02786953812818105</v>
       </c>
       <c r="M12" t="n">
-        <v>14.88965012328876</v>
+        <v>14.82829108536016</v>
       </c>
       <c r="N12" t="n">
-        <v>343.8205700591661</v>
+        <v>341.8542223423296</v>
       </c>
       <c r="O12" t="n">
-        <v>18.54239925304075</v>
+        <v>18.48930021234794</v>
       </c>
       <c r="P12" t="n">
-        <v>397.6851667147391</v>
+        <v>397.7918707603939</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30769,28 +30969,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3019777961708424</v>
+        <v>0.3226436740969411</v>
       </c>
       <c r="J13" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K13" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01497755503644416</v>
+        <v>0.01724064081442223</v>
       </c>
       <c r="M13" t="n">
-        <v>14.80052049587557</v>
+        <v>14.80713491653219</v>
       </c>
       <c r="N13" t="n">
-        <v>316.2830140880556</v>
+        <v>315.59025026364</v>
       </c>
       <c r="O13" t="n">
-        <v>17.78434744622517</v>
+        <v>17.76485998435225</v>
       </c>
       <c r="P13" t="n">
-        <v>391.0716086838353</v>
+        <v>390.8504982831524</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30847,28 +31047,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09009381201089527</v>
+        <v>0.1304945843440053</v>
       </c>
       <c r="J14" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K14" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001270270521861905</v>
+        <v>0.002657635371176692</v>
       </c>
       <c r="M14" t="n">
-        <v>15.80527556815294</v>
+        <v>15.92736868007364</v>
       </c>
       <c r="N14" t="n">
-        <v>335.6130587352362</v>
+        <v>338.9323305835033</v>
       </c>
       <c r="O14" t="n">
-        <v>18.31974505104359</v>
+        <v>18.41011489870455</v>
       </c>
       <c r="P14" t="n">
-        <v>391.7100636228641</v>
+        <v>391.2774709868207</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30925,28 +31125,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3985298708078454</v>
+        <v>-0.3401221631842142</v>
       </c>
       <c r="J15" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K15" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02002558167500801</v>
+        <v>0.01447417924061256</v>
       </c>
       <c r="M15" t="n">
-        <v>16.73054207977808</v>
+        <v>16.95322132529278</v>
       </c>
       <c r="N15" t="n">
-        <v>420.3790396344438</v>
+        <v>429.6405523923106</v>
       </c>
       <c r="O15" t="n">
-        <v>20.5031470665955</v>
+        <v>20.72777248988204</v>
       </c>
       <c r="P15" t="n">
-        <v>395.7480791434305</v>
+        <v>395.1360576445595</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31003,28 +31203,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4304894885683343</v>
+        <v>-0.3597553516817452</v>
       </c>
       <c r="J16" t="n">
+        <v>296</v>
+      </c>
+      <c r="K16" t="n">
         <v>294</v>
       </c>
-      <c r="K16" t="n">
-        <v>292</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02854491200681253</v>
+        <v>0.01941411972417417</v>
       </c>
       <c r="M16" t="n">
-        <v>14.2673540070675</v>
+        <v>14.58464540142172</v>
       </c>
       <c r="N16" t="n">
-        <v>340.4071281730144</v>
+        <v>355.8129050963565</v>
       </c>
       <c r="O16" t="n">
-        <v>18.45012542431661</v>
+        <v>18.86300360749466</v>
       </c>
       <c r="P16" t="n">
-        <v>392.962626483499</v>
+        <v>392.2194678645274</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31081,28 +31281,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.57404740297072</v>
+        <v>-0.4988725357128098</v>
       </c>
       <c r="J17" t="n">
+        <v>296</v>
+      </c>
+      <c r="K17" t="n">
         <v>294</v>
       </c>
-      <c r="K17" t="n">
-        <v>292</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04857370299664987</v>
+        <v>0.03567068886308311</v>
       </c>
       <c r="M17" t="n">
-        <v>14.5142342975085</v>
+        <v>14.81277630680505</v>
       </c>
       <c r="N17" t="n">
-        <v>349.3369518143527</v>
+        <v>367.1821050431446</v>
       </c>
       <c r="O17" t="n">
-        <v>18.6905578251253</v>
+        <v>19.1619963741554</v>
       </c>
       <c r="P17" t="n">
-        <v>395.3481958070145</v>
+        <v>394.5583898452869</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31159,28 +31359,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.851674033889908</v>
+        <v>-0.7708479302321266</v>
       </c>
       <c r="J18" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K18" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08312088572079479</v>
+        <v>0.06677820193605155</v>
       </c>
       <c r="M18" t="n">
-        <v>16.48224352151805</v>
+        <v>16.75258665616752</v>
       </c>
       <c r="N18" t="n">
-        <v>433.9498782292302</v>
+        <v>454.15468033423</v>
       </c>
       <c r="O18" t="n">
-        <v>20.83146366027194</v>
+        <v>21.31090519743894</v>
       </c>
       <c r="P18" t="n">
-        <v>403.8065234903734</v>
+        <v>402.9597718034705</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31237,28 +31437,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6598098135843611</v>
+        <v>-0.5856703241403015</v>
       </c>
       <c r="J19" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K19" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06736074813737258</v>
+        <v>0.05173257863407354</v>
       </c>
       <c r="M19" t="n">
-        <v>13.76019240760347</v>
+        <v>13.98117247779372</v>
       </c>
       <c r="N19" t="n">
-        <v>325.8056259280597</v>
+        <v>342.7080064790499</v>
       </c>
       <c r="O19" t="n">
-        <v>18.05008659059728</v>
+        <v>18.51237441494337</v>
       </c>
       <c r="P19" t="n">
-        <v>400.9828865693177</v>
+        <v>400.2050679560494</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31315,28 +31515,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5440199599740158</v>
+        <v>-0.4895904293533222</v>
       </c>
       <c r="J20" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K20" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04920480656417969</v>
+        <v>0.03950296725702018</v>
       </c>
       <c r="M20" t="n">
-        <v>14.08461132423787</v>
+        <v>14.25626071907763</v>
       </c>
       <c r="N20" t="n">
-        <v>309.1173398828584</v>
+        <v>317.6751597390208</v>
       </c>
       <c r="O20" t="n">
-        <v>17.58173313080535</v>
+        <v>17.8234441042976</v>
       </c>
       <c r="P20" t="n">
-        <v>393.4914627542626</v>
+        <v>392.9202407814171</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31393,28 +31593,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2696746465176035</v>
+        <v>-0.217353083589955</v>
       </c>
       <c r="J21" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K21" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01357939842504141</v>
+        <v>0.008698674503537118</v>
       </c>
       <c r="M21" t="n">
-        <v>13.87467866584777</v>
+        <v>14.02180433694458</v>
       </c>
       <c r="N21" t="n">
-        <v>285.5460058717599</v>
+        <v>293.4508201650997</v>
       </c>
       <c r="O21" t="n">
-        <v>16.89810657652981</v>
+        <v>17.13040630472902</v>
       </c>
       <c r="P21" t="n">
-        <v>386.3194787502723</v>
+        <v>385.7703804501618</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31471,28 +31671,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1529728101781225</v>
+        <v>-0.09193909013693985</v>
       </c>
       <c r="J22" t="n">
+        <v>296</v>
+      </c>
+      <c r="K22" t="n">
         <v>294</v>
       </c>
-      <c r="K22" t="n">
-        <v>292</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.003462724122472616</v>
+        <v>0.001227343201961606</v>
       </c>
       <c r="M22" t="n">
-        <v>15.94207134783232</v>
+        <v>16.16190650560214</v>
       </c>
       <c r="N22" t="n">
-        <v>363.9151885578813</v>
+        <v>374.8001300954397</v>
       </c>
       <c r="O22" t="n">
-        <v>19.07656123513568</v>
+        <v>19.35975542447372</v>
       </c>
       <c r="P22" t="n">
-        <v>379.0139161775402</v>
+        <v>378.3715982278734</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31549,28 +31749,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08080239569447664</v>
+        <v>0.1487211092164311</v>
       </c>
       <c r="J23" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K23" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0009861424284988152</v>
+        <v>0.003233240321866337</v>
       </c>
       <c r="M23" t="n">
-        <v>15.81796472287114</v>
+        <v>16.10729199885007</v>
       </c>
       <c r="N23" t="n">
-        <v>357.8316753128159</v>
+        <v>371.9478633512661</v>
       </c>
       <c r="O23" t="n">
-        <v>18.9164392873716</v>
+        <v>19.28594989496929</v>
       </c>
       <c r="P23" t="n">
-        <v>372.4954441362569</v>
+        <v>371.7802979554402</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31627,28 +31827,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2126084023805689</v>
+        <v>0.2650987412656109</v>
       </c>
       <c r="J24" t="n">
+        <v>296</v>
+      </c>
+      <c r="K24" t="n">
         <v>294</v>
       </c>
-      <c r="K24" t="n">
-        <v>292</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.007193397119558242</v>
+        <v>0.01098716394613575</v>
       </c>
       <c r="M24" t="n">
-        <v>15.40107166655839</v>
+        <v>15.5450252528725</v>
       </c>
       <c r="N24" t="n">
-        <v>338.582767712936</v>
+        <v>346.1813748256491</v>
       </c>
       <c r="O24" t="n">
-        <v>18.40061867745039</v>
+        <v>18.60594998449821</v>
       </c>
       <c r="P24" t="n">
-        <v>367.6771483455974</v>
+        <v>367.1264781880913</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31705,28 +31905,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3224809843003908</v>
+        <v>0.3491138738789474</v>
       </c>
       <c r="J25" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K25" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01935388856126918</v>
+        <v>0.02274487886485888</v>
       </c>
       <c r="M25" t="n">
-        <v>14.30595652618484</v>
+        <v>14.33423037031712</v>
       </c>
       <c r="N25" t="n">
-        <v>285.633116514706</v>
+        <v>286.2418950949516</v>
       </c>
       <c r="O25" t="n">
-        <v>16.90068390671532</v>
+        <v>16.91868479211524</v>
       </c>
       <c r="P25" t="n">
-        <v>369.826515797594</v>
+        <v>369.5472483911105</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31783,28 +31983,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3749351889332069</v>
+        <v>0.3780090238615927</v>
       </c>
       <c r="J26" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K26" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0226632795168995</v>
+        <v>0.02337062765600439</v>
       </c>
       <c r="M26" t="n">
-        <v>15.12919251754491</v>
+        <v>15.03865986831127</v>
       </c>
       <c r="N26" t="n">
-        <v>327.8865209351009</v>
+        <v>325.7054913007652</v>
       </c>
       <c r="O26" t="n">
-        <v>18.10763708867341</v>
+        <v>18.04731257835263</v>
       </c>
       <c r="P26" t="n">
-        <v>365.6156288214194</v>
+        <v>365.583405570248</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31861,28 +32061,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.259687311797831</v>
+        <v>0.2609270852378237</v>
       </c>
       <c r="J27" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K27" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01138589552684088</v>
+        <v>0.01167985100068536</v>
       </c>
       <c r="M27" t="n">
-        <v>15.10920590806998</v>
+        <v>15.00019602741561</v>
       </c>
       <c r="N27" t="n">
-        <v>316.7019714732708</v>
+        <v>314.2389486127003</v>
       </c>
       <c r="O27" t="n">
-        <v>17.79612237183344</v>
+        <v>17.72678618962559</v>
       </c>
       <c r="P27" t="n">
-        <v>362.5601770508035</v>
+        <v>362.5473279543033</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31920,7 +32120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB295"/>
+  <dimension ref="A1:AB297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72981,22 +73181,22 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>-37.79671722569258,174.84033158051975</t>
+          <t>-37.796778836771445,174.8402402052601</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>-37.796366583156626,174.83946781419712</t>
+          <t>-37.7964207841306,174.83938742806583</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>-37.795867967125325,174.83881797046982</t>
+          <t>-37.79592521569235,174.83873191126858</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>-37.79535345150113,174.83818915745113</t>
+          <t>-37.795393066511124,174.8381286274265</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -73051,12 +73251,12 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>-37.78775606281865,174.8353947921826</t>
+          <t>-37.78776006991694,174.8353297047634</t>
         </is>
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>-37.7870665088053,174.8354082025816</t>
+          <t>-37.78707491886792,174.83531810956998</t>
         </is>
       </c>
       <c r="T295" t="inlineStr">
@@ -73096,12 +73296,296 @@
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>-37.781375202370455,174.83514053317214</t>
+          <t>-37.78138461458975,174.83508131313747</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>-37.79765863781032,174.84170295930602</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>-37.797114128706475,174.84112672953833</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>-37.79683887250202,174.84015116615282</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-37.796476151917645,174.8393053112177</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-37.79596168340349,174.8386770908786</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-37.795410437482985,174.83810208529675</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-37.79480375155216,174.83761956378706</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-37.79413785352337,174.83713781693913</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-37.79344259599566,174.83671290728586</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-37.79274277566095,174.83642010950783</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-37.79204476839529,174.83616324798075</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-37.79132589871106,174.83584359989342</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-37.79059069192369,174.83568326769714</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-37.78988274032485,174.83556472676966</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-37.78917054295493,174.83544438898232</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-37.78845831852574,174.83538397857183</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>-37.78776109433457,174.8353130650218</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>-37.787077666070076,174.83528867993286</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>-37.78636891120576,174.83536231504814</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>-37.785663020461335,174.83526064341862</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>-37.78495941053423,174.83511513726995</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>-37.78425812426638,174.83494811299894</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>-37.783540424258476,174.8349636818882</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>-37.78282977118615,174.83502437142567</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>-37.7821070386797,174.8350917264752</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>-37.78139308910036,174.83502799282923</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>-37.79765863781032,174.84170295930602</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>-37.797113136853625,174.84112820053963</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>-37.79691361077086,174.84004032134726</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-37.79653741231389,174.83921445470878</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-37.79601215930635,174.83860121240804</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-37.79544609668787,174.83804759943345</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-37.79481714450787,174.8375990429672</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-37.794122567852185,174.837168088226</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-37.79341821473756,174.8367915988911</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-37.792731737207504,174.83646465441484</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-37.79203881802794,174.83619133096568</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-37.79132496996155,174.83585123146761</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-37.7905921510687,174.83566188756785</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-37.78988441212197,174.8355384701305</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-37.78917144234648,174.8354278512555</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-37.78845996774933,174.83535077729977</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>-37.78776334525764,174.8352765028666</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>-37.78708119216172,174.83525090625707</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>-37.78637734174953,174.83528791036727</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>-37.78567087427086,174.83519106709937</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>-37.784965448835266,174.8350594566664</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>-37.78426229762737,174.8349081542659</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>-37.783540518306424,174.83496278141854</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>-37.78283180036617,174.83500891457797</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>-37.78211101314494,174.83506667858174</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>-37.781393672938414,174.8350243194046</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0225/nzd0225.xlsx
+++ b/data/nzd0225/nzd0225.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB297"/>
+  <dimension ref="A1:AB298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26776,10 +26776,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>337.23</v>
+        <v>344.07</v>
       </c>
       <c r="C297" t="n">
-        <v>337.4</v>
+        <v>352.89</v>
       </c>
       <c r="D297" t="n">
         <v>396.87</v>
@@ -26856,6 +26856,96 @@
       <c r="AB297" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>350.24</v>
+      </c>
+      <c r="C298" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="D298" t="n">
+        <v>403.36</v>
+      </c>
+      <c r="E298" t="n">
+        <v>431.52</v>
+      </c>
+      <c r="F298" t="n">
+        <v>434.9</v>
+      </c>
+      <c r="G298" t="n">
+        <v>431.42</v>
+      </c>
+      <c r="H298" t="n">
+        <v>417.36</v>
+      </c>
+      <c r="I298" t="n">
+        <v>395.81</v>
+      </c>
+      <c r="J298" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="K298" t="n">
+        <v>398.03</v>
+      </c>
+      <c r="L298" t="n">
+        <v>400.41</v>
+      </c>
+      <c r="M298" t="n">
+        <v>413.39</v>
+      </c>
+      <c r="N298" t="n">
+        <v>424.52</v>
+      </c>
+      <c r="O298" t="n">
+        <v>428.47</v>
+      </c>
+      <c r="P298" t="n">
+        <v>432.76</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>435.86</v>
+      </c>
+      <c r="R298" t="n">
+        <v>438.64</v>
+      </c>
+      <c r="S298" t="n">
+        <v>435.71</v>
+      </c>
+      <c r="T298" t="n">
+        <v>422.35</v>
+      </c>
+      <c r="U298" t="n">
+        <v>420.32</v>
+      </c>
+      <c r="V298" t="n">
+        <v>421.03</v>
+      </c>
+      <c r="W298" t="n">
+        <v>423.29</v>
+      </c>
+      <c r="X298" t="n">
+        <v>410.01</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26870,7 +26960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B307"/>
+  <dimension ref="A1:B308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29943,6 +30033,16 @@
       </c>
       <c r="B307" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -30111,28 +30211,28 @@
         <v>0.0269</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.362050930616238</v>
+        <v>-1.446125731053353</v>
       </c>
       <c r="J2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02279813195732761</v>
+        <v>0.02558242453600024</v>
       </c>
       <c r="M2" t="n">
-        <v>56.75747399850619</v>
+        <v>57.09823110115454</v>
       </c>
       <c r="N2" t="n">
-        <v>4504.250204456939</v>
+        <v>4533.723886173388</v>
       </c>
       <c r="O2" t="n">
-        <v>67.11371100197738</v>
+        <v>67.33293314696299</v>
       </c>
       <c r="P2" t="n">
-        <v>506.2676769927519</v>
+        <v>507.1241210401299</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30189,28 +30289,28 @@
         <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.619674426484752</v>
+        <v>-1.687935197251909</v>
       </c>
       <c r="J3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02900799773787044</v>
+        <v>0.03151679026536569</v>
       </c>
       <c r="M3" t="n">
-        <v>55.38010334198445</v>
+        <v>55.63952178056842</v>
       </c>
       <c r="N3" t="n">
-        <v>4563.086826393947</v>
+        <v>4571.328401362174</v>
       </c>
       <c r="O3" t="n">
-        <v>67.55062417471764</v>
+        <v>67.61159960659246</v>
       </c>
       <c r="P3" t="n">
-        <v>510.0324867899444</v>
+        <v>510.7766163624184</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30267,28 +30367,28 @@
         <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9881007836160862</v>
+        <v>-1.039516938469886</v>
       </c>
       <c r="J4" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01180001307693601</v>
+        <v>0.0131029996770633</v>
       </c>
       <c r="M4" t="n">
-        <v>54.22038349000984</v>
+        <v>54.36681962794761</v>
       </c>
       <c r="N4" t="n">
-        <v>4507.089487975888</v>
+        <v>4507.724316595734</v>
       </c>
       <c r="O4" t="n">
-        <v>67.13486045249434</v>
+        <v>67.13958829629307</v>
       </c>
       <c r="P4" t="n">
-        <v>498.4315201672937</v>
+        <v>498.9670415036695</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30345,28 +30445,28 @@
         <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1893542057072193</v>
+        <v>-0.2256733557548926</v>
       </c>
       <c r="J5" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K5" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000532434611560606</v>
+        <v>0.0007605681100241179</v>
       </c>
       <c r="M5" t="n">
-        <v>49.75771497201286</v>
+        <v>49.80425966793968</v>
       </c>
       <c r="N5" t="n">
-        <v>3785.923820089566</v>
+        <v>3780.610598814837</v>
       </c>
       <c r="O5" t="n">
-        <v>61.5298612064871</v>
+        <v>61.48667009047438</v>
       </c>
       <c r="P5" t="n">
-        <v>485.6127863794122</v>
+        <v>485.9899925008736</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30423,28 +30523,28 @@
         <v>0.0364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6691249484044222</v>
+        <v>0.6358335835762214</v>
       </c>
       <c r="J6" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K6" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007480353521815086</v>
+        <v>0.006796296789401857</v>
       </c>
       <c r="M6" t="n">
-        <v>45.22365247637875</v>
+        <v>45.29648071716814</v>
       </c>
       <c r="N6" t="n">
-        <v>3253.41488257526</v>
+        <v>3249.767294694354</v>
       </c>
       <c r="O6" t="n">
-        <v>57.03871389306793</v>
+        <v>57.00673025787705</v>
       </c>
       <c r="P6" t="n">
-        <v>464.4054532350663</v>
+        <v>464.7558634277307</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30501,28 +30601,28 @@
         <v>0.0332</v>
       </c>
       <c r="I7" t="n">
-        <v>1.170780039465304</v>
+        <v>1.130409208312856</v>
       </c>
       <c r="J7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K7" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02518770055329733</v>
+        <v>0.02360821127494028</v>
       </c>
       <c r="M7" t="n">
-        <v>41.2738082293768</v>
+        <v>41.30323931872518</v>
       </c>
       <c r="N7" t="n">
-        <v>2864.541584045893</v>
+        <v>2865.863663740479</v>
       </c>
       <c r="O7" t="n">
-        <v>53.52141238836932</v>
+        <v>53.53376190536659</v>
       </c>
       <c r="P7" t="n">
-        <v>457.578415499064</v>
+        <v>458.0093660772992</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30579,28 +30679,28 @@
         <v>0.0314</v>
       </c>
       <c r="I8" t="n">
-        <v>1.122727432577356</v>
+        <v>1.083200395686793</v>
       </c>
       <c r="J8" t="n">
+        <v>297</v>
+      </c>
+      <c r="K8" t="n">
         <v>296</v>
       </c>
-      <c r="K8" t="n">
-        <v>295</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04007995515846419</v>
+        <v>0.03744134474954774</v>
       </c>
       <c r="M8" t="n">
-        <v>32.6087171884943</v>
+        <v>32.66811577204692</v>
       </c>
       <c r="N8" t="n">
-        <v>1648.917842706072</v>
+        <v>1654.542634545359</v>
       </c>
       <c r="O8" t="n">
-        <v>40.60686940292334</v>
+        <v>40.67606955625579</v>
       </c>
       <c r="P8" t="n">
-        <v>445.4162416130805</v>
+        <v>445.8326112363686</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30657,28 +30757,28 @@
         <v>0.0318</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5244720833262663</v>
+        <v>0.4886959637302933</v>
       </c>
       <c r="J9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01565026562868355</v>
+        <v>0.01358888333828567</v>
       </c>
       <c r="M9" t="n">
-        <v>25.15059170879113</v>
+        <v>25.20953757292626</v>
       </c>
       <c r="N9" t="n">
-        <v>937.1448425344421</v>
+        <v>943.0309530975144</v>
       </c>
       <c r="O9" t="n">
-        <v>30.61282153827775</v>
+        <v>30.70880904720199</v>
       </c>
       <c r="P9" t="n">
-        <v>433.8146933625634</v>
+        <v>434.1944121910454</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30735,28 +30835,28 @@
         <v>0.0321</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3898730864770262</v>
+        <v>0.3628957852667103</v>
       </c>
       <c r="J10" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K10" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L10" t="n">
-        <v>0.017105845007373</v>
+        <v>0.0148047845402286</v>
       </c>
       <c r="M10" t="n">
-        <v>18.32494425537778</v>
+        <v>18.40247938906513</v>
       </c>
       <c r="N10" t="n">
-        <v>477.2388459047399</v>
+        <v>480.8362723195767</v>
       </c>
       <c r="O10" t="n">
-        <v>21.84579698488339</v>
+        <v>21.92797921194693</v>
       </c>
       <c r="P10" t="n">
-        <v>420.3037210510379</v>
+        <v>420.5902773898257</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30813,28 +30913,28 @@
         <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>0.481238313098035</v>
+        <v>0.4623306132074742</v>
       </c>
       <c r="J11" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K11" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03346773031349759</v>
+        <v>0.03098413816772827</v>
       </c>
       <c r="M11" t="n">
-        <v>15.07933850834921</v>
+        <v>15.11232258374058</v>
       </c>
       <c r="N11" t="n">
-        <v>366.4041653867354</v>
+        <v>367.7487356107347</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1416865867858</v>
+        <v>19.17677594411361</v>
       </c>
       <c r="P11" t="n">
-        <v>412.998585996187</v>
+        <v>413.1981825668963</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30891,28 +30991,28 @@
         <v>0.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4253438591259873</v>
+        <v>0.4193860602577649</v>
       </c>
       <c r="J12" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K12" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02786953812818105</v>
+        <v>0.02729714794477789</v>
       </c>
       <c r="M12" t="n">
-        <v>14.82829108536016</v>
+        <v>14.80121733750358</v>
       </c>
       <c r="N12" t="n">
-        <v>341.8542223423296</v>
+        <v>340.9480743071924</v>
       </c>
       <c r="O12" t="n">
-        <v>18.48930021234794</v>
+        <v>18.46477929213324</v>
       </c>
       <c r="P12" t="n">
-        <v>397.7918707603939</v>
+        <v>397.8551147357966</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30969,28 +31069,28 @@
         <v>0.037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3226436740969411</v>
+        <v>0.3323868447702226</v>
       </c>
       <c r="J13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K13" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01724064081442223</v>
+        <v>0.01837871091286114</v>
       </c>
       <c r="M13" t="n">
-        <v>14.80713491653219</v>
+        <v>14.8069766738803</v>
       </c>
       <c r="N13" t="n">
-        <v>315.59025026364</v>
+        <v>315.1715391329367</v>
       </c>
       <c r="O13" t="n">
-        <v>17.76485998435225</v>
+        <v>17.75307125916349</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8504982831524</v>
+        <v>390.7456765545676</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31047,28 +31147,28 @@
         <v>0.0426</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1304945843440053</v>
+        <v>0.1512727717076769</v>
       </c>
       <c r="J14" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K14" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002657635371176692</v>
+        <v>0.003564148955144897</v>
       </c>
       <c r="M14" t="n">
-        <v>15.92736868007364</v>
+        <v>15.98966822387551</v>
       </c>
       <c r="N14" t="n">
-        <v>338.9323305835033</v>
+        <v>340.7615809228072</v>
       </c>
       <c r="O14" t="n">
-        <v>18.41011489870455</v>
+        <v>18.45972862538361</v>
       </c>
       <c r="P14" t="n">
-        <v>391.2774709868207</v>
+        <v>391.0537755261044</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31125,28 +31225,28 @@
         <v>0.0531</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3401221631842142</v>
+        <v>-0.3111336564729647</v>
       </c>
       <c r="J15" t="n">
+        <v>297</v>
+      </c>
+      <c r="K15" t="n">
         <v>296</v>
       </c>
-      <c r="K15" t="n">
-        <v>295</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.01447417924061256</v>
+        <v>0.0120658053919126</v>
       </c>
       <c r="M15" t="n">
-        <v>16.95322132529278</v>
+        <v>17.06436757950606</v>
       </c>
       <c r="N15" t="n">
-        <v>429.6405523923106</v>
+        <v>434.1875619935354</v>
       </c>
       <c r="O15" t="n">
-        <v>20.72777248988204</v>
+        <v>20.83716780163599</v>
       </c>
       <c r="P15" t="n">
-        <v>395.1360576445595</v>
+        <v>394.8306140523908</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31203,28 +31303,28 @@
         <v>0.0553</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3597553516817452</v>
+        <v>-0.3253873131681992</v>
       </c>
       <c r="J16" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K16" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01941411972417417</v>
+        <v>0.01569216142400243</v>
       </c>
       <c r="M16" t="n">
-        <v>14.58464540142172</v>
+        <v>14.73678662910473</v>
       </c>
       <c r="N16" t="n">
-        <v>355.8129050963565</v>
+        <v>363.0222166564312</v>
       </c>
       <c r="O16" t="n">
-        <v>18.86300360749466</v>
+        <v>19.053141910363</v>
       </c>
       <c r="P16" t="n">
-        <v>392.2194678645274</v>
+        <v>391.8563701120902</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31281,28 +31381,28 @@
         <v>0.0517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4988725357128098</v>
+        <v>-0.4616275416245005</v>
       </c>
       <c r="J17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K17" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03567068886308311</v>
+        <v>0.03013122046253303</v>
       </c>
       <c r="M17" t="n">
-        <v>14.81277630680505</v>
+        <v>14.96077722417131</v>
       </c>
       <c r="N17" t="n">
-        <v>367.1821050431446</v>
+        <v>375.9152053420282</v>
       </c>
       <c r="O17" t="n">
-        <v>19.1619963741554</v>
+        <v>19.38853283108416</v>
       </c>
       <c r="P17" t="n">
-        <v>394.5583898452869</v>
+        <v>394.1648908152559</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31359,28 +31459,28 @@
         <v>0.0452</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7708479302321266</v>
+        <v>-0.7326060796480643</v>
       </c>
       <c r="J18" t="n">
+        <v>297</v>
+      </c>
+      <c r="K18" t="n">
         <v>296</v>
       </c>
-      <c r="K18" t="n">
-        <v>295</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.06677820193605155</v>
+        <v>0.05983541466789133</v>
       </c>
       <c r="M18" t="n">
-        <v>16.75258665616752</v>
+        <v>16.88029180240541</v>
       </c>
       <c r="N18" t="n">
-        <v>454.15468033423</v>
+        <v>463.1593528181</v>
       </c>
       <c r="O18" t="n">
-        <v>21.31090519743894</v>
+        <v>21.52113734954777</v>
       </c>
       <c r="P18" t="n">
-        <v>402.9597718034705</v>
+        <v>402.5568242555689</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31437,28 +31537,28 @@
         <v>0.0382</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5856703241403015</v>
+        <v>-0.5508936164388492</v>
       </c>
       <c r="J19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05173257863407354</v>
+        <v>0.04528258384030137</v>
       </c>
       <c r="M19" t="n">
-        <v>13.98117247779372</v>
+        <v>14.09058161388116</v>
       </c>
       <c r="N19" t="n">
-        <v>342.7080064790499</v>
+        <v>350.2382863151467</v>
       </c>
       <c r="O19" t="n">
-        <v>18.51237441494337</v>
+        <v>18.71465431994796</v>
       </c>
       <c r="P19" t="n">
-        <v>400.2050679560494</v>
+        <v>399.83808242357</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31515,28 +31615,28 @@
         <v>0.0357</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4895904293533222</v>
+        <v>-0.4606903618296257</v>
       </c>
       <c r="J20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03950296725702018</v>
+        <v>0.03475924375118289</v>
       </c>
       <c r="M20" t="n">
-        <v>14.25626071907763</v>
+        <v>14.3484591397654</v>
       </c>
       <c r="N20" t="n">
-        <v>317.6751597390208</v>
+        <v>322.6027603733837</v>
       </c>
       <c r="O20" t="n">
-        <v>17.8234441042976</v>
+        <v>17.9611458535747</v>
       </c>
       <c r="P20" t="n">
-        <v>392.9202407814171</v>
+        <v>392.6152692251697</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31593,28 +31693,28 @@
         <v>0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.217353083589955</v>
+        <v>-0.1898928571612616</v>
       </c>
       <c r="J21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008698674503537118</v>
+        <v>0.006582579718174442</v>
       </c>
       <c r="M21" t="n">
-        <v>14.02180433694458</v>
+        <v>14.10382017821298</v>
       </c>
       <c r="N21" t="n">
-        <v>293.4508201650997</v>
+        <v>297.8772914440252</v>
       </c>
       <c r="O21" t="n">
-        <v>17.13040630472902</v>
+        <v>17.25912197778396</v>
       </c>
       <c r="P21" t="n">
-        <v>385.7703804501618</v>
+        <v>385.4806029961127</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31671,28 +31771,28 @@
         <v>0.0461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09193909013693985</v>
+        <v>-0.0611463456958763</v>
       </c>
       <c r="J22" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K22" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001227343201961606</v>
+        <v>0.000537575885875996</v>
       </c>
       <c r="M22" t="n">
-        <v>16.16190650560214</v>
+        <v>16.27181832936999</v>
       </c>
       <c r="N22" t="n">
-        <v>374.8001300954397</v>
+        <v>380.3496358619474</v>
       </c>
       <c r="O22" t="n">
-        <v>19.35975542447372</v>
+        <v>19.50255459835833</v>
       </c>
       <c r="P22" t="n">
-        <v>378.3715982278734</v>
+        <v>378.045727999103</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31749,28 +31849,28 @@
         <v>0.0481</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1487211092164311</v>
+        <v>0.1812054919664189</v>
       </c>
       <c r="J23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K23" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003233240321866337</v>
+        <v>0.004731988626041073</v>
       </c>
       <c r="M23" t="n">
-        <v>16.10729199885007</v>
+        <v>16.25081812039547</v>
       </c>
       <c r="N23" t="n">
-        <v>371.9478633512661</v>
+        <v>378.2919887068296</v>
       </c>
       <c r="O23" t="n">
-        <v>19.28594989496929</v>
+        <v>19.44972978493093</v>
       </c>
       <c r="P23" t="n">
-        <v>371.7802979554402</v>
+        <v>371.4363325671624</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31827,28 +31927,28 @@
         <v>0.0515</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2650987412656109</v>
+        <v>0.2895097213089846</v>
       </c>
       <c r="J24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K24" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01098716394613575</v>
+        <v>0.01301386537841598</v>
       </c>
       <c r="M24" t="n">
-        <v>15.5450252528725</v>
+        <v>15.60752190759772</v>
       </c>
       <c r="N24" t="n">
-        <v>346.1813748256491</v>
+        <v>349.3152519415615</v>
       </c>
       <c r="O24" t="n">
-        <v>18.60594998449821</v>
+        <v>18.68997731249456</v>
       </c>
       <c r="P24" t="n">
-        <v>367.1264781880913</v>
+        <v>366.8689380115968</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31905,28 +32005,28 @@
         <v>0.0471</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3491138738789474</v>
+        <v>0.3625629319182518</v>
       </c>
       <c r="J25" t="n">
+        <v>297</v>
+      </c>
+      <c r="K25" t="n">
         <v>296</v>
       </c>
-      <c r="K25" t="n">
-        <v>295</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.02274487886485888</v>
+        <v>0.02455964462325511</v>
       </c>
       <c r="M25" t="n">
-        <v>14.33423037031712</v>
+        <v>14.34821379867639</v>
       </c>
       <c r="N25" t="n">
-        <v>286.2418950949516</v>
+        <v>286.5789563607117</v>
       </c>
       <c r="O25" t="n">
-        <v>16.91868479211524</v>
+        <v>16.928643074999</v>
       </c>
       <c r="P25" t="n">
-        <v>369.5472483911105</v>
+        <v>369.4054351059797</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31983,28 +32083,28 @@
         <v>0.0504</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3780090238615927</v>
+        <v>0.3814961991729841</v>
       </c>
       <c r="J26" t="n">
+        <v>297</v>
+      </c>
+      <c r="K26" t="n">
         <v>296</v>
       </c>
-      <c r="K26" t="n">
-        <v>295</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.02337062765600439</v>
+        <v>0.02396546179473902</v>
       </c>
       <c r="M26" t="n">
-        <v>15.03865986831127</v>
+        <v>15.00128870800196</v>
       </c>
       <c r="N26" t="n">
-        <v>325.7054913007652</v>
+        <v>324.6919386416501</v>
       </c>
       <c r="O26" t="n">
-        <v>18.04731257835263</v>
+        <v>18.01921026686936</v>
       </c>
       <c r="P26" t="n">
-        <v>365.583405570248</v>
+        <v>365.5466622028079</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32061,28 +32161,28 @@
         <v>0.0523</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2609270852378237</v>
+        <v>0.2615062924585529</v>
       </c>
       <c r="J27" t="n">
+        <v>297</v>
+      </c>
+      <c r="K27" t="n">
         <v>296</v>
       </c>
-      <c r="K27" t="n">
-        <v>295</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01167985100068536</v>
+        <v>0.01182002481498945</v>
       </c>
       <c r="M27" t="n">
-        <v>15.00019602741561</v>
+        <v>14.95222132452185</v>
       </c>
       <c r="N27" t="n">
-        <v>314.2389486127003</v>
+        <v>313.1797252852315</v>
       </c>
       <c r="O27" t="n">
-        <v>17.72678618962559</v>
+        <v>17.69688462089391</v>
       </c>
       <c r="P27" t="n">
-        <v>362.5473279543033</v>
+        <v>362.5412250137181</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32120,7 +32220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB297"/>
+  <dimension ref="A1:AB298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73455,12 +73555,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>-37.79765863781032,174.84170295930602</t>
+          <t>-37.79769854547542,174.84164377289517</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-37.797113136853625,174.84112820053963</t>
+          <t>-37.79720351208022,174.84099416620143</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -73586,6 +73686,148 @@
       <c r="AB297" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-37.79773454403204,174.8415903839287</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>-37.79726734059037,174.84089950262964</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-37.7969514757887,174.83998416335456</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-37.796569267693535,174.8391672092645</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-37.7960389601395,174.83856092368245</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-37.79546226371495,174.83802289682208</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-37.79482738954433,174.837583345412</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-37.79411685990975,174.83717939205772</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-37.79340995655786,174.83681825248718</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-37.7927275742828,174.8364814535854</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-37.792038492617024,174.83619286675378</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-37.79132476509027,174.83585291490306</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-37.79059254480559,174.83565611832648</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-37.78988396534917,174.8355454869911</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-37.78917073392182,174.83544087754726</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-37.78845947242037,174.83536074901306</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-37.78776278078574,174.83528567170455</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-37.78708117111046,174.83525113177154</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-37.78637726533998,174.83528858473002</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>-37.785670354068266,174.83519567554754</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>-37.784964045999985,174.83507239256508</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>-37.784258911915806,174.83494057149196</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>-37.783538284665866,174.83498416757277</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>-37.78283174154939,174.83500936260253</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>-37.78211422804189,174.8350464176169</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>-37.78139804287423,174.83499682437574</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
